--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>128.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.0%</t>
+          <t>448.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-572.7%</t>
+          <t>-573.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-245.2%</t>
+          <t>-245.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-90.1%</t>
+          <t>-97.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-233.7%</t>
+          <t>-227.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.3%</t>
+          <t>-152.8%</t>
         </is>
       </c>
     </row>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.510202914464877</v>
+        <v>-8.57385130623268</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2913017398115083</v>
+        <v>-0.3167610965186292</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.893204303207508</v>
+        <v>-8.956852694975311</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4446043966301447</v>
+        <v>-0.470063753337266</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.050603183420629</v>
+        <v>-9.114251575188431</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.504992432743963</v>
+        <v>-0.5304517894510838</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.41013350592463</v>
+        <v>-9.473781897692433</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6434542584475134</v>
+        <v>-0.6689136151546347</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.460482569378852</v>
+        <v>-9.524130961146655</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6556778638720249</v>
+        <v>-0.6811372205791457</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.67963153745305</v>
+        <v>-9.743279929220853</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7402957004799346</v>
+        <v>-0.7657550571870559</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.675940612496639</v>
+        <v>-9.739589004264442</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7388193304973707</v>
+        <v>-0.7642786872044915</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.880198787826503</v>
+        <v>-9.943847179594306</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8150094035106736</v>
+        <v>-0.8404687602177949</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09823655945768</v>
+        <v>-10.16188495122548</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8977419576787082</v>
+        <v>-0.9232013143858295</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.02476672779023</v>
+        <v>-10.08841511955803</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.852982323518308</v>
+        <v>-0.8784416802254293</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19989114517677</v>
+        <v>-10.26353953694458</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9084768697254084</v>
+        <v>-0.9339362264325297</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43434323919126</v>
+        <v>-10.49799163095907</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.0094768722328</v>
+        <v>-1.034936228939922</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.7221470837285</v>
+        <v>-10.78579547549631</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.131270600821672</v>
+        <v>-1.156729957528793</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.77493323932883</v>
+        <v>-10.83858163109663</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.151269273223246</v>
+        <v>-1.176728629930367</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00696215906509</v>
+        <v>-11.07061055083289</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.241387112488636</v>
+        <v>-1.266846469195757</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95494664509628</v>
+        <v>-11.01859503686408</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.21659057121471</v>
+        <v>-1.242049927921832</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.0966184868204</v>
+        <v>-11.1602668785882</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.2747345348031</v>
+        <v>-1.300193891510221</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04702764239556</v>
+        <v>-11.11067603416337</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.239844786868294</v>
+        <v>-1.265304143575416</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84787553515847</v>
+        <v>-10.91152392692627</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.173235077620137</v>
+        <v>-1.198694434327259</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62203038243905</v>
+        <v>-10.68567877420686</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.073317943496164</v>
+        <v>-1.098777300203285</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49745172610146</v>
+        <v>-10.56110011786926</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.022347336405069</v>
+        <v>-1.04780669311219</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55034701414575</v>
+        <v>-10.61399540591355</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.040871677460675</v>
+        <v>-1.066331034167797</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.266438283217</v>
+        <v>-10.3300866749848</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9215744808505395</v>
+        <v>-0.9470338375576608</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19507189060735</v>
+        <v>-10.25872028237515</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9027651862005452</v>
+        <v>-0.9282245429076665</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.931235023403282</v>
+        <v>-9.994883415171085</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8071139206318252</v>
+        <v>-0.8325732773389465</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663993222534884</v>
+        <v>-9.727641614302687</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7020517607838399</v>
+        <v>-0.7275111174909612</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.566086183858394</v>
+        <v>-9.629734575626197</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6631892602867047</v>
+        <v>-0.6886486169938255</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.542132642882436</v>
+        <v>-9.605781034650239</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6529393377508277</v>
+        <v>-0.678398694457949</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.278072704559639</v>
+        <v>-9.341721096327442</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.560575678583461</v>
+        <v>-0.5860350352905823</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309723</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570993081054802</v>
+        <v>-8.634641472822604</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.280530862841827</v>
+        <v>-0.3059902195489483</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.530808782688611</v>
+        <v>-8.594457174456414</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2641135196075095</v>
+        <v>-0.2895728763146308</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450738987150807</v>
+        <v>-8.51438737891861</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2327187801716306</v>
+        <v>-0.2581781368787519</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.217257764921207</v>
+        <v>-8.28090615668901</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1314018624419386</v>
+        <v>-0.1568612191490599</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067591373913693</v>
+        <v>-8.131239765681496</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07442751635189193</v>
+        <v>-0.09988687305901323</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.935315900282807</v>
+        <v>-7.998964292050609</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02614984015251043</v>
+        <v>-0.05160919685963172</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744716225609654</v>
+        <v>-7.808364617377457</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05290509040438707</v>
+        <v>0.02744573369726622</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495716426926073</v>
+        <v>-7.559364818693876</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1654113511014783</v>
+        <v>0.1399519943943575</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.601306416699178</v>
+        <v>-7.66495480846698</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.004800574406981895</v>
+        <v>-0.03025993111410319</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.620041318817774</v>
+        <v>-7.683689710585577</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.0362498066226653</v>
+        <v>0.01079044991554445</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.472101277410175</v>
+        <v>-7.535749669177978</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02445309950246255</v>
+        <v>-0.0499124562095834</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.447872641021203</v>
+        <v>-7.511521032789005</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02347563120035145</v>
+        <v>-0.04893498790747275</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.404324234250512</v>
+        <v>-7.467972626018315</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01301688058716843</v>
+        <v>-0.03847623729428973</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.162175840796654</v>
+        <v>-7.225824232564457</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09830483117551791</v>
+        <v>0.07284547446839662</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.098946469028306</v>
+        <v>-7.162594860796109</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1181287003420524</v>
+        <v>0.09266934363493107</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.975655334211175</v>
+        <v>-7.039303725978978</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1649432482794815</v>
+        <v>0.1394838915723602</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.954506135307732</v>
+        <v>-7.018154527075534</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1811039060781838</v>
+        <v>0.155644549371063</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.710740693324287</v>
+        <v>-6.77438908509209</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2743907912186123</v>
+        <v>0.248931434511491</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.563843665606417</v>
+        <v>-6.627492057374219</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3352739162257765</v>
+        <v>0.3098145595186557</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.313993271657342</v>
+        <v>-6.377641663425145</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4279561487891086</v>
+        <v>0.4024967920819873</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.13810117918991</v>
+        <v>-6.201749570957713</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5019121092967302</v>
+        <v>0.476452752589609</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.966654716167446</v>
+        <v>-6.030303107935249</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5838182005602692</v>
+        <v>0.5583588438531479</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.741621716498623</v>
+        <v>-5.805270108266426</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6728518780440953</v>
+        <v>0.6473925213369744</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.677985974264689</v>
+        <v>-5.741634366032492</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7030009759919866</v>
+        <v>0.6775416192848653</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.584985933058791</v>
+        <v>-5.648634324826594</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7213952512581416</v>
+        <v>0.6959358945510203</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.34455543625393</v>
+        <v>-5.408203828021733</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.819310526604963</v>
+        <v>0.7938511698978417</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.272312868082736</v>
+        <v>-5.335961259850539</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.852136867708261</v>
+        <v>0.8266775110011397</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349963</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.15637301845755</v>
+        <v>-5.220021410225353</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8991913914756751</v>
+        <v>0.8737320347685542</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.047568132977823</v>
+        <v>-5.111216524745626</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9397114168875595</v>
+        <v>0.9142520601804383</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.827547334940813</v>
+        <v>-4.891195726708616</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.029298773112978</v>
+        <v>1.003839416405857</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.694679645877535</v>
+        <v>-4.758328037645338</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.098340031540112</v>
+        <v>1.072880674832991</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.535164542358165</v>
+        <v>-4.598812934125968</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.163291917388162</v>
+        <v>1.137832560681041</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.390492397258428</v>
+        <v>-4.454140789026231</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.231248877989497</v>
+        <v>1.205789521282376</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.45036722461612</v>
+        <v>-4.514015616383923</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.193336438447846</v>
+        <v>1.167877081740725</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.363567726837111</v>
+        <v>-4.427216118604914</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.250456730882016</v>
+        <v>1.224997374174894</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.366037433298917</v>
+        <v>-4.42968582506672</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.249541249670705</v>
+        <v>1.224081892963584</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.434407619622927</v>
+        <v>-4.49805601139073</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.233200097615803</v>
+        <v>1.207740740908682</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.312991189996451</v>
+        <v>-4.376639581764254</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.272203378098285</v>
+        <v>1.246744021391164</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.343984349325156</v>
+        <v>-4.407632741092959</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.08451567940719</v>
+        <v>1.059056322700069</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.168510089532687</v>
+        <v>-4.232158481300489</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.159272615315965</v>
+        <v>1.133813258608844</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695442</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.279446342173935</v>
+        <v>-4.343094733941738</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.090640143020673</v>
+        <v>1.065180786313552</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.482472919717169</v>
+        <v>-4.546121311484971</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.012560897223285</v>
+        <v>0.9871015405161641</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.324547320781876</v>
+        <v>-4.388195712549678</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.085903523229535</v>
+        <v>1.060444166522414</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.238303857755498</v>
+        <v>-4.301952249523301</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.115347179013946</v>
+        <v>1.089887822306825</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.239486942406559</v>
+        <v>-4.303135334174362</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.106649720598047</v>
+        <v>1.081190363890926</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.116359235412476</v>
+        <v>-4.180007627180279</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.156452676428782</v>
+        <v>1.130993319721661</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.023548753961617</v>
+        <v>-4.087197145729419</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.122849560900491</v>
+        <v>1.09739020419337</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.974985701740586</v>
+        <v>-4.03863409350839</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.144148257713504</v>
+        <v>1.118688901006383</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862314483504336</v>
+        <v>-3.925962875272139</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.184292453519727</v>
+        <v>1.158833096812606</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.749937482321664</v>
+        <v>-3.813585874089467</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.234734549823464</v>
+        <v>1.209275193116342</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.948172051208394</v>
+        <v>-4.011820442976197</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.166937924037311</v>
+        <v>1.141478567330189</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.031173332233672</v>
+        <v>-4.094821724001476</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9720931316278525</v>
+        <v>0.946633774920731</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.871979060177096</v>
+        <v>-3.9356274519449</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.155920501169688</v>
+        <v>1.130461144462567</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.958577643158199</v>
+        <v>-4.022226034926003</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.13579409407957</v>
+        <v>1.110334737372449</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.920193980600048</v>
+        <v>-3.983842372367852</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.1485670004452</v>
+        <v>1.123107643738078</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.743077650564882</v>
+        <v>-3.806726042332686</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.216142561304568</v>
+        <v>1.190683204597446</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.713375526588588</v>
+        <v>-3.777023918356393</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.228706802656998</v>
+        <v>1.203247445949877</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.53400010534982</v>
+        <v>-3.597648497117625</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.29424394645892</v>
+        <v>1.268784589751798</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452229</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.579014318870426</v>
+        <v>-3.642662710638231</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.257045716382267</v>
+        <v>1.231586359675146</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.846018829142862</v>
+        <v>-3.909667220910666</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.155935474612239</v>
+        <v>1.130476117905117</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.280146500599932</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.134806049601777</v>
+        <v>-4.198454441369582</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.039624508325174</v>
+        <v>1.014165151618052</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3812326206989324</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.102330463431005</v>
+        <v>-4.16597885519881</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.0502147043478</v>
+        <v>1.024755347640678</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3812326206989324</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.709506867848103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.083292335723708</v>
+        <v>-4.146940727491512</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.054354674638964</v>
+        <v>1.028895317931842</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4394162320301269</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.100038200980083</v>
+        <v>-4.163686592747887</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.225238197475094</v>
+        <v>1.199778840767972</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4394162320301269</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.152358581580875</v>
+        <v>-4.216006973348679</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.205143374220911</v>
+        <v>1.179684017513789</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4044693720212548</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.296681487505793</v>
+        <v>-4.360329879273598</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.153422742247869</v>
+        <v>1.127963385540748</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4044693720212548</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.148938517270791</v>
+        <v>-4.212586909038595</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.291672578133892</v>
+        <v>1.266213221426771</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2366620147863716</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651169</v>
+        <v>3.802242353651171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.250953199802012</v>
+        <v>-4.314601591569817</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.253660326652885</v>
+        <v>1.228200969945763</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2366620147863716</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.515529936035889</v>
+        <v>3.716320703868498</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.111273248998023</v>
+        <v>-4.116086316767229</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.310194655366139</v>
+        <v>1.308269428258457</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.09698206398238257</v>
+        <v>-0.03814673998378326</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.896871140889666</v>
+        <v>2.932172335288826</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.2%</t>
+          <t>-579.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-245.4%</t>
+          <t>-247.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-97.2%</t>
+          <t>-96.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-227.8%</t>
+          <t>-234.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.8%</t>
+          <t>-156.5%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.71417556397837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.116086316767229</v>
+        <v>-4.177992247475724</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.308269428258457</v>
+        <v>1.283507055975058</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.03814673998378326</v>
+        <v>-0.1000526706922791</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.932172335288826</v>
+        <v>2.895028776863728</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.6%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-52.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.5%</t>
+          <t>449.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-579.4%</t>
+          <t>-549.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-247.9%</t>
+          <t>-235.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-96.1%</t>
+          <t>-100.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-234.0%</t>
+          <t>-214.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.5%</t>
+          <t>-144.9%</t>
         </is>
       </c>
     </row>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.57385130623268</v>
+        <v>-8.510202914464877</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3167610965186292</v>
+        <v>-0.2913017398115083</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.956852694975311</v>
+        <v>-8.893204303207508</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.470063753337266</v>
+        <v>-0.4446043966301447</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.114251575188431</v>
+        <v>-9.050603183420629</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5304517894510838</v>
+        <v>-0.504992432743963</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.473781897692433</v>
+        <v>-9.41013350592463</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6689136151546347</v>
+        <v>-0.6434542584475134</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.524130961146655</v>
+        <v>-9.460482569378852</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6811372205791457</v>
+        <v>-0.6556778638720249</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.743279929220853</v>
+        <v>-9.67963153745305</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7657550571870559</v>
+        <v>-0.7402957004799346</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.739589004264442</v>
+        <v>-9.675940612496639</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7642786872044915</v>
+        <v>-0.7388193304973707</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.943847179594306</v>
+        <v>-9.880198787826503</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8404687602177949</v>
+        <v>-0.8150094035106736</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.16188495122548</v>
+        <v>-10.09823655945768</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9232013143858295</v>
+        <v>-0.8977419576787082</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.08841511955803</v>
+        <v>-10.02476672779023</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8784416802254293</v>
+        <v>-0.852982323518308</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.26353953694458</v>
+        <v>-10.19989114517677</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9339362264325297</v>
+        <v>-0.9084768697254084</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.49799163095907</v>
+        <v>-10.43434323919126</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.034936228939922</v>
+        <v>-1.0094768722328</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.78579547549631</v>
+        <v>-10.7221470837285</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.156729957528793</v>
+        <v>-1.131270600821672</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.83858163109663</v>
+        <v>-10.77493323932883</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.176728629930367</v>
+        <v>-1.151269273223246</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.07061055083289</v>
+        <v>-11.00696215906509</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.266846469195757</v>
+        <v>-1.241387112488636</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.01859503686408</v>
+        <v>-10.95494664509628</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.242049927921832</v>
+        <v>-1.21659057121471</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.1602668785882</v>
+        <v>-11.0966184868204</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.300193891510221</v>
+        <v>-1.2747345348031</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.11067603416337</v>
+        <v>-11.04702764239556</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.265304143575416</v>
+        <v>-1.239844786868294</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.91152392692627</v>
+        <v>-10.84787553515847</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.198694434327259</v>
+        <v>-1.173235077620137</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.68567877420686</v>
+        <v>-10.62203038243905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.098777300203285</v>
+        <v>-1.073317943496164</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.56110011786926</v>
+        <v>-10.49745172610146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.04780669311219</v>
+        <v>-1.022347336405069</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.61399540591355</v>
+        <v>-10.55034701414575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.066331034167797</v>
+        <v>-1.040871677460675</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.3300866749848</v>
+        <v>-10.266438283217</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9470338375576608</v>
+        <v>-0.9215744808505395</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.25872028237515</v>
+        <v>-10.19507189060735</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9282245429076665</v>
+        <v>-0.9027651862005452</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.994883415171085</v>
+        <v>-9.931235023403282</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8325732773389465</v>
+        <v>-0.8071139206318252</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.727641614302687</v>
+        <v>-9.663993222534884</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7275111174909612</v>
+        <v>-0.7020517607838399</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.629734575626197</v>
+        <v>-9.566086183858394</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6886486169938255</v>
+        <v>-0.6631892602867047</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.605781034650239</v>
+        <v>-9.542132642882436</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.678398694457949</v>
+        <v>-0.6529393377508277</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.341721096327442</v>
+        <v>-9.278072704559639</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5860350352905823</v>
+        <v>-0.560575678583461</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.634641472822604</v>
+        <v>-8.570993081054802</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3059902195489483</v>
+        <v>-0.280530862841827</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.594457174456414</v>
+        <v>-8.530808782688611</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2895728763146308</v>
+        <v>-0.2641135196075095</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.51438737891861</v>
+        <v>-8.450738987150807</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2581781368787519</v>
+        <v>-0.2327187801716306</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.28090615668901</v>
+        <v>-8.217257764921207</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1568612191490599</v>
+        <v>-0.1314018624419386</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.131239765681496</v>
+        <v>-8.067591373913693</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09988687305901323</v>
+        <v>-0.07442751635189193</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.998964292050609</v>
+        <v>-7.935315900282807</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05160919685963172</v>
+        <v>-0.02614984015251043</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.808364617377457</v>
+        <v>-7.744716225609654</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02744573369726622</v>
+        <v>0.05290509040438707</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.559364818693876</v>
+        <v>-7.495716426926073</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1399519943943575</v>
+        <v>0.1654113511014783</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.66495480846698</v>
+        <v>-7.601306416699178</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03025993111410319</v>
+        <v>-0.004800574406981895</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.683689710585577</v>
+        <v>-7.620041318817774</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01079044991554445</v>
+        <v>0.0362498066226653</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.535749669177978</v>
+        <v>-7.472101277410175</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0499124562095834</v>
+        <v>-0.02445309950246255</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.511521032789005</v>
+        <v>-7.447872641021203</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04893498790747275</v>
+        <v>-0.02347563120035145</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.467972626018315</v>
+        <v>-7.404324234250512</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03847623729428973</v>
+        <v>-0.01301688058716843</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.225824232564457</v>
+        <v>-7.162175840796654</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.07284547446839662</v>
+        <v>0.09830483117551791</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.162594860796109</v>
+        <v>-7.098946469028306</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09266934363493107</v>
+        <v>0.1181287003420524</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.039303725978978</v>
+        <v>-6.975655334211175</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1394838915723602</v>
+        <v>0.1649432482794815</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.018154527075534</v>
+        <v>-6.954506135307732</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.155644549371063</v>
+        <v>0.1811039060781838</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.77438908509209</v>
+        <v>-6.710740693324287</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.248931434511491</v>
+        <v>0.2743907912186123</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.627492057374219</v>
+        <v>-6.563843665606417</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3098145595186557</v>
+        <v>0.3352739162257765</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.377641663425145</v>
+        <v>-6.313993271657342</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4024967920819873</v>
+        <v>0.4279561487891086</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.201749570957713</v>
+        <v>-6.13810117918991</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.476452752589609</v>
+        <v>0.5019121092967302</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.030303107935249</v>
+        <v>-5.966654716167446</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5583588438531479</v>
+        <v>0.5838182005602692</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.805270108266426</v>
+        <v>-5.741621716498623</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6473925213369744</v>
+        <v>0.6728518780440953</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.741634366032492</v>
+        <v>-5.677985974264689</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6775416192848653</v>
+        <v>0.7030009759919866</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.648634324826594</v>
+        <v>-5.584985933058791</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6959358945510203</v>
+        <v>0.7213952512581416</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.408203828021733</v>
+        <v>-5.34455543625393</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7938511698978417</v>
+        <v>0.819310526604963</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.335961259850539</v>
+        <v>-5.272312868082736</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8266775110011397</v>
+        <v>0.852136867708261</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.220021410225353</v>
+        <v>-5.15637301845755</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8737320347685542</v>
+        <v>0.8991913914756751</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.111216524745626</v>
+        <v>-5.047568132977823</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9142520601804383</v>
+        <v>0.9397114168875595</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.891195726708616</v>
+        <v>-4.827547334940813</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.003839416405857</v>
+        <v>1.029298773112978</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.758328037645338</v>
+        <v>-4.694679645877535</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.072880674832991</v>
+        <v>1.098340031540112</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.598812934125968</v>
+        <v>-4.535164542358165</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.137832560681041</v>
+        <v>1.163291917388162</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.454140789026231</v>
+        <v>-4.390492397258428</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.205789521282376</v>
+        <v>1.231248877989497</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.514015616383923</v>
+        <v>-4.45036722461612</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.167877081740725</v>
+        <v>1.193336438447846</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.427216118604914</v>
+        <v>-4.363567726837111</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.224997374174894</v>
+        <v>1.250456730882016</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.42968582506672</v>
+        <v>-4.366037433298917</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.224081892963584</v>
+        <v>1.249541249670705</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.49805601139073</v>
+        <v>-4.434407619622927</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.207740740908682</v>
+        <v>1.233200097615803</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.376639581764254</v>
+        <v>-4.312991189996451</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.246744021391164</v>
+        <v>1.272203378098285</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.407632741092959</v>
+        <v>-4.343984349325156</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.059056322700069</v>
+        <v>1.08451567940719</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.232158481300489</v>
+        <v>-4.168510089532687</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.133813258608844</v>
+        <v>1.159272615315965</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.343094733941738</v>
+        <v>-4.279446342173935</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.065180786313552</v>
+        <v>1.090640143020673</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.546121311484971</v>
+        <v>-4.482472919717169</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9871015405161641</v>
+        <v>1.012560897223285</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.388195712549678</v>
+        <v>-4.324547320781876</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.060444166522414</v>
+        <v>1.085903523229535</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.301952249523301</v>
+        <v>-4.238303857755498</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.089887822306825</v>
+        <v>1.115347179013946</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.303135334174362</v>
+        <v>-4.239486942406559</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.081190363890926</v>
+        <v>1.106649720598047</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.180007627180279</v>
+        <v>-4.116359235412476</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.130993319721661</v>
+        <v>1.156452676428782</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.087197145729419</v>
+        <v>-4.023548753961617</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.09739020419337</v>
+        <v>1.122849560900491</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.03863409350839</v>
+        <v>-3.974985701740586</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.118688901006383</v>
+        <v>1.144148257713504</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.925962875272139</v>
+        <v>-3.862314483504336</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.158833096812606</v>
+        <v>1.184292453519727</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.813585874089467</v>
+        <v>-3.749937482321664</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.209275193116342</v>
+        <v>1.234734549823464</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.011820442976197</v>
+        <v>-3.948172051208394</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.141478567330189</v>
+        <v>1.166937924037311</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.094821724001476</v>
+        <v>-4.031173332233672</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.946633774920731</v>
+        <v>0.9720931316278525</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.9356274519449</v>
+        <v>-3.871979060177096</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.130461144462567</v>
+        <v>1.155920501169688</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.022226034926003</v>
+        <v>-3.958577643158199</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.110334737372449</v>
+        <v>1.13579409407957</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.983842372367852</v>
+        <v>-3.920193980600048</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.123107643738078</v>
+        <v>1.1485670004452</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.806726042332686</v>
+        <v>-3.743077650564882</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.190683204597446</v>
+        <v>1.216142561304568</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.777023918356393</v>
+        <v>-3.713375526588588</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.203247445949877</v>
+        <v>1.228706802656998</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.597648497117625</v>
+        <v>-3.53400010534982</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.268784589751798</v>
+        <v>1.29424394645892</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.642662710638231</v>
+        <v>-3.579014318870426</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.231586359675146</v>
+        <v>1.257045716382267</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.909667220910666</v>
+        <v>-3.611150553950606</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.130476117905117</v>
+        <v>1.249882784689141</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.280146500599932</v>
+        <v>-0.08628808793723597</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.526611530223172</v>
+        <v>2.64292657782079</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.198454441369582</v>
+        <v>-3.899937774409521</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.014165151618052</v>
+        <v>1.133571818402077</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.1873742080362363</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.465163780060273</v>
+        <v>2.581478827657891</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.16597885519881</v>
+        <v>-3.867462188238749</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.024755347640678</v>
+        <v>1.144162014424702</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.1873742080362363</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.46276374161459</v>
+        <v>2.579078789212208</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848103</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.146940727491512</v>
+        <v>-3.848424060531451</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.028895317931842</v>
+        <v>1.148301984715866</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.2455578193674309</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.424378294024118</v>
+        <v>2.540693341621736</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.163686592747887</v>
+        <v>-3.865169925787827</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.199778840767972</v>
+        <v>1.319185507551996</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.2455578193674309</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.601960162962799</v>
+        <v>2.718275210560416</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.216006973348679</v>
+        <v>-3.917490306388618</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.179684017513789</v>
+        <v>1.299090684297813</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.2106109593585587</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.623761607954255</v>
+        <v>2.740076655551873</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.360329879273598</v>
+        <v>-4.061813212313537</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.127963385540748</v>
+        <v>1.247370052324772</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.2106109593585587</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.629770138351181</v>
+        <v>2.746085185948799</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989909</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.212586909038595</v>
+        <v>-3.914070242078535</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.266213221426771</v>
+        <v>1.385619888210795</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.04280360212367557</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.809607200484133</v>
+        <v>2.925922248081751</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651171</v>
+        <v>3.802242353651169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.314601591569817</v>
+        <v>-4.016084924609756</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.228200969945763</v>
+        <v>1.347607636729787</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.04280360212367557</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.812400822015614</v>
+        <v>2.928715869613232</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.716320703868498</v>
+        <v>3.878917764801745</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.177992247475724</v>
+        <v>-3.879475580515664</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.283507055975058</v>
+        <v>1.402913722759082</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1000526706922791</v>
+        <v>0.09380574197041691</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.895028776863728</v>
+        <v>3.011343824461346</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-19.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>128.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.2%</t>
+          <t>448.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-549.5%</t>
+          <t>-579.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-235.9%</t>
+          <t>-247.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-100.4%</t>
+          <t>-96.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-214.6%</t>
+          <t>-234.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-144.9%</t>
+          <t>-154.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1968"/>
+  <dimension ref="A1:G1969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.510202914464877</v>
+        <v>-8.57385130623268</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2913017398115083</v>
+        <v>-0.3167610965186292</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.893204303207508</v>
+        <v>-8.956852694975311</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4446043966301447</v>
+        <v>-0.470063753337266</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.050603183420629</v>
+        <v>-9.114251575188431</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.504992432743963</v>
+        <v>-0.5304517894510838</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.41013350592463</v>
+        <v>-9.473781897692433</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6434542584475134</v>
+        <v>-0.6689136151546347</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.460482569378852</v>
+        <v>-9.524130961146655</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6556778638720249</v>
+        <v>-0.6811372205791457</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.67963153745305</v>
+        <v>-9.743279929220853</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7402957004799346</v>
+        <v>-0.7657550571870559</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.675940612496639</v>
+        <v>-9.739589004264442</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7388193304973707</v>
+        <v>-0.7642786872044915</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.880198787826503</v>
+        <v>-9.943847179594306</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8150094035106736</v>
+        <v>-0.8404687602177949</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09823655945768</v>
+        <v>-10.16188495122548</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8977419576787082</v>
+        <v>-0.9232013143858295</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.02476672779023</v>
+        <v>-10.08841511955803</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.852982323518308</v>
+        <v>-0.8784416802254293</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19989114517677</v>
+        <v>-10.26353953694458</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9084768697254084</v>
+        <v>-0.9339362264325297</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43434323919126</v>
+        <v>-10.49799163095907</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.0094768722328</v>
+        <v>-1.034936228939922</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.7221470837285</v>
+        <v>-10.78579547549631</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.131270600821672</v>
+        <v>-1.156729957528793</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.77493323932883</v>
+        <v>-10.83858163109663</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.151269273223246</v>
+        <v>-1.176728629930367</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00696215906509</v>
+        <v>-11.07061055083289</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.241387112488636</v>
+        <v>-1.266846469195757</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95494664509628</v>
+        <v>-11.01859503686408</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.21659057121471</v>
+        <v>-1.242049927921832</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.0966184868204</v>
+        <v>-11.1602668785882</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.2747345348031</v>
+        <v>-1.300193891510221</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04702764239556</v>
+        <v>-11.11067603416337</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.239844786868294</v>
+        <v>-1.265304143575416</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84787553515847</v>
+        <v>-10.91152392692627</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.173235077620137</v>
+        <v>-1.198694434327259</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62203038243905</v>
+        <v>-10.68567877420686</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.073317943496164</v>
+        <v>-1.098777300203285</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49745172610146</v>
+        <v>-10.56110011786926</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.022347336405069</v>
+        <v>-1.04780669311219</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55034701414575</v>
+        <v>-10.61399540591355</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.040871677460675</v>
+        <v>-1.066331034167797</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.266438283217</v>
+        <v>-10.3300866749848</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9215744808505395</v>
+        <v>-0.9470338375576608</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19507189060735</v>
+        <v>-10.25872028237515</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9027651862005452</v>
+        <v>-0.9282245429076665</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.931235023403282</v>
+        <v>-9.994883415171085</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8071139206318252</v>
+        <v>-0.8325732773389465</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663993222534884</v>
+        <v>-9.727641614302687</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7020517607838399</v>
+        <v>-0.7275111174909612</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.566086183858394</v>
+        <v>-9.629734575626197</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6631892602867047</v>
+        <v>-0.6886486169938255</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.542132642882436</v>
+        <v>-9.605781034650239</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6529393377508277</v>
+        <v>-0.678398694457949</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.278072704559639</v>
+        <v>-9.341721096327442</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.560575678583461</v>
+        <v>-0.5860350352905823</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570993081054802</v>
+        <v>-8.634641472822604</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.280530862841827</v>
+        <v>-0.3059902195489483</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.530808782688611</v>
+        <v>-8.594457174456414</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2641135196075095</v>
+        <v>-0.2895728763146308</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450738987150807</v>
+        <v>-8.51438737891861</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2327187801716306</v>
+        <v>-0.2581781368787519</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.217257764921207</v>
+        <v>-8.28090615668901</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1314018624419386</v>
+        <v>-0.1568612191490599</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067591373913693</v>
+        <v>-8.131239765681496</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07442751635189193</v>
+        <v>-0.09988687305901323</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.935315900282807</v>
+        <v>-7.998964292050609</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02614984015251043</v>
+        <v>-0.05160919685963172</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744716225609654</v>
+        <v>-7.808364617377457</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05290509040438707</v>
+        <v>0.02744573369726622</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495716426926073</v>
+        <v>-7.559364818693876</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1654113511014783</v>
+        <v>0.1399519943943575</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.601306416699178</v>
+        <v>-7.66495480846698</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.004800574406981895</v>
+        <v>-0.03025993111410319</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.620041318817774</v>
+        <v>-7.683689710585577</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.0362498066226653</v>
+        <v>0.01079044991554445</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.472101277410175</v>
+        <v>-7.535749669177978</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02445309950246255</v>
+        <v>-0.0499124562095834</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.447872641021203</v>
+        <v>-7.511521032789005</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02347563120035145</v>
+        <v>-0.04893498790747275</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.404324234250512</v>
+        <v>-7.467972626018315</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01301688058716843</v>
+        <v>-0.03847623729428973</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.162175840796654</v>
+        <v>-7.225824232564457</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09830483117551791</v>
+        <v>0.07284547446839662</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.098946469028306</v>
+        <v>-7.162594860796109</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1181287003420524</v>
+        <v>0.09266934363493107</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.975655334211175</v>
+        <v>-7.039303725978978</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1649432482794815</v>
+        <v>0.1394838915723602</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.954506135307732</v>
+        <v>-7.018154527075534</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1811039060781838</v>
+        <v>0.155644549371063</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.710740693324287</v>
+        <v>-6.77438908509209</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2743907912186123</v>
+        <v>0.248931434511491</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.563843665606417</v>
+        <v>-6.627492057374219</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3352739162257765</v>
+        <v>0.3098145595186557</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.313993271657342</v>
+        <v>-6.377641663425145</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4279561487891086</v>
+        <v>0.4024967920819873</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.13810117918991</v>
+        <v>-6.201749570957713</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5019121092967302</v>
+        <v>0.476452752589609</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.966654716167446</v>
+        <v>-6.030303107935249</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5838182005602692</v>
+        <v>0.5583588438531479</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.741621716498623</v>
+        <v>-5.805270108266426</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6728518780440953</v>
+        <v>0.6473925213369744</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.677985974264689</v>
+        <v>-5.741634366032492</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7030009759919866</v>
+        <v>0.6775416192848653</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.584985933058791</v>
+        <v>-5.648634324826594</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7213952512581416</v>
+        <v>0.6959358945510203</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.34455543625393</v>
+        <v>-5.408203828021733</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.819310526604963</v>
+        <v>0.7938511698978417</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.272312868082736</v>
+        <v>-5.335961259850539</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.852136867708261</v>
+        <v>0.8266775110011397</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.15637301845755</v>
+        <v>-5.220021410225353</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8991913914756751</v>
+        <v>0.8737320347685542</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.047568132977823</v>
+        <v>-5.111216524745626</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9397114168875595</v>
+        <v>0.9142520601804383</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.827547334940813</v>
+        <v>-4.891195726708616</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.029298773112978</v>
+        <v>1.003839416405857</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.694679645877535</v>
+        <v>-4.758328037645338</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.098340031540112</v>
+        <v>1.072880674832991</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.535164542358165</v>
+        <v>-4.598812934125968</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.163291917388162</v>
+        <v>1.137832560681041</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.390492397258428</v>
+        <v>-4.454140789026231</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.231248877989497</v>
+        <v>1.205789521282376</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.45036722461612</v>
+        <v>-4.514015616383923</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.193336438447846</v>
+        <v>1.167877081740725</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.363567726837111</v>
+        <v>-4.427216118604914</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.250456730882016</v>
+        <v>1.224997374174894</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.366037433298917</v>
+        <v>-4.42968582506672</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.249541249670705</v>
+        <v>1.224081892963584</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.434407619622927</v>
+        <v>-4.49805601139073</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.233200097615803</v>
+        <v>1.207740740908682</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.312991189996451</v>
+        <v>-4.376639581764254</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.272203378098285</v>
+        <v>1.246744021391164</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.343984349325156</v>
+        <v>-4.407632741092959</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.08451567940719</v>
+        <v>1.059056322700069</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.168510089532687</v>
+        <v>-4.232158481300489</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.159272615315965</v>
+        <v>1.133813258608844</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.279446342173935</v>
+        <v>-4.343094733941738</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.090640143020673</v>
+        <v>1.065180786313552</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.482472919717169</v>
+        <v>-4.546121311484971</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.012560897223285</v>
+        <v>0.9871015405161641</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.324547320781876</v>
+        <v>-4.388195712549678</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.085903523229535</v>
+        <v>1.060444166522414</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.238303857755498</v>
+        <v>-4.301952249523301</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.115347179013946</v>
+        <v>1.089887822306825</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.239486942406559</v>
+        <v>-4.303135334174362</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.106649720598047</v>
+        <v>1.081190363890926</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.116359235412476</v>
+        <v>-4.180007627180279</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.156452676428782</v>
+        <v>1.130993319721661</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.023548753961617</v>
+        <v>-4.087197145729419</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.122849560900491</v>
+        <v>1.09739020419337</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.974985701740586</v>
+        <v>-4.03863409350839</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.144148257713504</v>
+        <v>1.118688901006383</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862314483504336</v>
+        <v>-3.925962875272139</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.184292453519727</v>
+        <v>1.158833096812606</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.749937482321664</v>
+        <v>-3.813585874089467</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.234734549823464</v>
+        <v>1.209275193116342</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.948172051208394</v>
+        <v>-4.011820442976197</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.166937924037311</v>
+        <v>1.141478567330189</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.031173332233672</v>
+        <v>-4.094821724001476</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9720931316278525</v>
+        <v>0.946633774920731</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.871979060177096</v>
+        <v>-3.9356274519449</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.155920501169688</v>
+        <v>1.130461144462567</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.958577643158199</v>
+        <v>-4.022226034926003</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.13579409407957</v>
+        <v>1.110334737372449</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.920193980600048</v>
+        <v>-3.983842372367852</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.1485670004452</v>
+        <v>1.123107643738078</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.743077650564882</v>
+        <v>-3.806726042332686</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.216142561304568</v>
+        <v>1.190683204597446</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.713375526588588</v>
+        <v>-3.777023918356393</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.228706802656998</v>
+        <v>1.203247445949877</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.53400010534982</v>
+        <v>-3.597648497117625</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.29424394645892</v>
+        <v>1.268784589751798</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.579014318870426</v>
+        <v>-3.642662710638231</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.257045716382267</v>
+        <v>1.231586359675146</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.611150553950606</v>
+        <v>-3.909667220910666</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.249882784689141</v>
+        <v>1.130476117905117</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08628808793723597</v>
+        <v>-0.280146500599932</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.64292657782079</v>
+        <v>2.526611530223172</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230808</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.899937774409521</v>
+        <v>-4.198454441369582</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.133571818402077</v>
+        <v>1.014165151618052</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1873742080362363</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.581478827657891</v>
+        <v>2.465163780060273</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285454</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.867462188238749</v>
+        <v>-4.16597885519881</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.144162014424702</v>
+        <v>1.024755347640678</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1873742080362363</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.579078789212208</v>
+        <v>2.46276374161459</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.709506867848103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.848424060531451</v>
+        <v>-4.146940727491512</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.148301984715866</v>
+        <v>1.028895317931842</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2455578193674309</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.540693341621736</v>
+        <v>2.424378294024118</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.865169925787827</v>
+        <v>-4.163686592747887</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.319185507551996</v>
+        <v>1.199778840767972</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2455578193674309</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.718275210560416</v>
+        <v>2.601960162962799</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.917490306388618</v>
+        <v>-4.216006973348679</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.299090684297813</v>
+        <v>1.179684017513789</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2106109593585587</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.740076655551873</v>
+        <v>2.623761607954255</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.061813212313537</v>
+        <v>-4.360329879273598</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.247370052324772</v>
+        <v>1.127963385540748</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2106109593585587</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.746085185948799</v>
+        <v>2.629770138351181</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.914070242078535</v>
+        <v>-4.212586909038595</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.385619888210795</v>
+        <v>1.266213221426771</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.04280360212367557</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.925922248081751</v>
+        <v>2.809607200484133</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651169</v>
+        <v>3.802242353651171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.016084924609756</v>
+        <v>-4.314601591569817</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.347607636729787</v>
+        <v>1.228200969945763</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.04280360212367557</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.928715869613232</v>
+        <v>2.812400822015614</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,45 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.878917764801745</v>
+        <v>3.805605409864728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.879475580515664</v>
+        <v>-4.177992247475724</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.402913722759082</v>
+        <v>1.283507055975058</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.09380574197041691</v>
+        <v>-0.1000526706922791</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.011343824461346</v>
+        <v>2.895028776863728</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="2" t="n">
+        <v>45431</v>
+      </c>
+      <c r="B1969" t="n">
+        <v>3.716619966915324</v>
+      </c>
+      <c r="C1969" t="n">
+        <v>2.921549617714755</v>
+      </c>
+      <c r="D1969" t="n">
+        <v>-4.177992247475724</v>
+      </c>
+      <c r="E1969" t="n">
+        <v>1.283507055975058</v>
+      </c>
+      <c r="F1969" t="n">
+        <v>-0.1000526706922791</v>
+      </c>
+      <c r="G1969" t="n">
+        <v>2.914613414701122</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-27.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.5%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-52.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.5%</t>
+          <t>446.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-579.4%</t>
+          <t>-560.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-247.9%</t>
+          <t>-240.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-96.1%</t>
+          <t>-139.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-234.0%</t>
+          <t>-227.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-154.6%</t>
+          <t>-162.7%</t>
         </is>
       </c>
     </row>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.57385130623268</v>
+        <v>-8.510202914464877</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3167610965186292</v>
+        <v>-0.2913017398115083</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.956852694975311</v>
+        <v>-8.893204303207508</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.470063753337266</v>
+        <v>-0.4446043966301447</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.114251575188431</v>
+        <v>-9.050603183420629</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5304517894510838</v>
+        <v>-0.504992432743963</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.473781897692433</v>
+        <v>-9.41013350592463</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6689136151546347</v>
+        <v>-0.6434542584475134</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.524130961146655</v>
+        <v>-9.460482569378852</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6811372205791457</v>
+        <v>-0.6556778638720249</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.743279929220853</v>
+        <v>-9.67963153745305</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7657550571870559</v>
+        <v>-0.7402957004799346</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.739589004264442</v>
+        <v>-9.675940612496639</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7642786872044915</v>
+        <v>-0.7388193304973707</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.943847179594306</v>
+        <v>-9.880198787826503</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8404687602177949</v>
+        <v>-0.8150094035106736</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.16188495122548</v>
+        <v>-10.09823655945768</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9232013143858295</v>
+        <v>-0.8977419576787082</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.08841511955803</v>
+        <v>-10.02476672779023</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8784416802254293</v>
+        <v>-0.852982323518308</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.26353953694458</v>
+        <v>-10.19989114517677</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9339362264325297</v>
+        <v>-0.9084768697254084</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.49799163095907</v>
+        <v>-10.43434323919126</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.034936228939922</v>
+        <v>-1.0094768722328</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.78579547549631</v>
+        <v>-10.7221470837285</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.156729957528793</v>
+        <v>-1.131270600821672</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.83858163109663</v>
+        <v>-10.77493323932883</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.176728629930367</v>
+        <v>-1.151269273223246</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.07061055083289</v>
+        <v>-11.00696215906509</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.266846469195757</v>
+        <v>-1.241387112488636</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.01859503686408</v>
+        <v>-10.95494664509628</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.242049927921832</v>
+        <v>-1.21659057121471</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.1602668785882</v>
+        <v>-11.0966184868204</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.300193891510221</v>
+        <v>-1.2747345348031</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.11067603416337</v>
+        <v>-11.04702764239556</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.265304143575416</v>
+        <v>-1.239844786868294</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.91152392692627</v>
+        <v>-10.84787553515847</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.198694434327259</v>
+        <v>-1.173235077620137</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.68567877420686</v>
+        <v>-10.62203038243905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.098777300203285</v>
+        <v>-1.073317943496164</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.56110011786926</v>
+        <v>-10.49745172610146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.04780669311219</v>
+        <v>-1.022347336405069</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.61399540591355</v>
+        <v>-10.55034701414575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.066331034167797</v>
+        <v>-1.040871677460675</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.3300866749848</v>
+        <v>-10.266438283217</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9470338375576608</v>
+        <v>-0.9215744808505395</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.25872028237515</v>
+        <v>-10.19507189060735</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9282245429076665</v>
+        <v>-0.9027651862005452</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.994883415171085</v>
+        <v>-9.931235023403282</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8325732773389465</v>
+        <v>-0.8071139206318252</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.727641614302687</v>
+        <v>-9.663993222534884</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7275111174909612</v>
+        <v>-0.7020517607838399</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.629734575626197</v>
+        <v>-9.566086183858394</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6886486169938255</v>
+        <v>-0.6631892602867047</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.605781034650239</v>
+        <v>-9.542132642882436</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.678398694457949</v>
+        <v>-0.6529393377508277</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.341721096327442</v>
+        <v>-9.278072704559639</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5860350352905823</v>
+        <v>-0.560575678583461</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.634641472822604</v>
+        <v>-8.570993081054802</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3059902195489483</v>
+        <v>-0.280530862841827</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.594457174456414</v>
+        <v>-8.530808782688611</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2895728763146308</v>
+        <v>-0.2641135196075095</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.51438737891861</v>
+        <v>-8.450738987150807</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2581781368787519</v>
+        <v>-0.2327187801716306</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.28090615668901</v>
+        <v>-8.217257764921207</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1568612191490599</v>
+        <v>-0.1314018624419386</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.131239765681496</v>
+        <v>-8.067591373913693</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09988687305901323</v>
+        <v>-0.07442751635189193</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.998964292050609</v>
+        <v>-7.935315900282807</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05160919685963172</v>
+        <v>-0.02614984015251043</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.808364617377457</v>
+        <v>-7.744716225609654</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02744573369726622</v>
+        <v>0.05290509040438707</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.559364818693876</v>
+        <v>-7.495716426926073</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1399519943943575</v>
+        <v>0.1654113511014783</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.66495480846698</v>
+        <v>-7.601306416699178</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03025993111410319</v>
+        <v>-0.004800574406981895</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.683689710585577</v>
+        <v>-7.620041318817774</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01079044991554445</v>
+        <v>0.0362498066226653</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.535749669177978</v>
+        <v>-7.472101277410175</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0499124562095834</v>
+        <v>-0.02445309950246255</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.511521032789005</v>
+        <v>-7.447872641021203</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04893498790747275</v>
+        <v>-0.02347563120035145</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.467972626018315</v>
+        <v>-7.404324234250512</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03847623729428973</v>
+        <v>-0.01301688058716843</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.225824232564457</v>
+        <v>-7.162175840796654</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.07284547446839662</v>
+        <v>0.09830483117551791</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.162594860796109</v>
+        <v>-7.098946469028306</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09266934363493107</v>
+        <v>0.1181287003420524</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.039303725978978</v>
+        <v>-6.975655334211175</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1394838915723602</v>
+        <v>0.1649432482794815</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.018154527075534</v>
+        <v>-6.954506135307732</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.155644549371063</v>
+        <v>0.1811039060781838</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.77438908509209</v>
+        <v>-6.710740693324287</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.248931434511491</v>
+        <v>0.2743907912186123</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.627492057374219</v>
+        <v>-6.563843665606417</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3098145595186557</v>
+        <v>0.3352739162257765</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.377641663425145</v>
+        <v>-6.313993271657342</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4024967920819873</v>
+        <v>0.4279561487891086</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.201749570957713</v>
+        <v>-6.13810117918991</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.476452752589609</v>
+        <v>0.5019121092967302</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.030303107935249</v>
+        <v>-5.966654716167446</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5583588438531479</v>
+        <v>0.5838182005602692</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.805270108266426</v>
+        <v>-5.741621716498623</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6473925213369744</v>
+        <v>0.6728518780440953</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.741634366032492</v>
+        <v>-5.677985974264689</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6775416192848653</v>
+        <v>0.7030009759919866</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.648634324826594</v>
+        <v>-5.584985933058791</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6959358945510203</v>
+        <v>0.7213952512581416</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.408203828021733</v>
+        <v>-5.34455543625393</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7938511698978417</v>
+        <v>0.819310526604963</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.335961259850539</v>
+        <v>-5.272312868082736</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8266775110011397</v>
+        <v>0.852136867708261</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.220021410225353</v>
+        <v>-5.15637301845755</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8737320347685542</v>
+        <v>0.8991913914756751</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.111216524745626</v>
+        <v>-5.047568132977823</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9142520601804383</v>
+        <v>0.9397114168875595</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.891195726708616</v>
+        <v>-4.935444747889435</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.003839416405857</v>
+        <v>0.9861398079335288</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.4494075036680273</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.7651863619573</v>
+        <v>2.691029629202234</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.758328037645338</v>
+        <v>-4.802577058826158</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.072880674832991</v>
+        <v>1.055181066360663</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.4494075036680273</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.781080544759124</v>
+        <v>2.706923812004058</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.598812934125968</v>
+        <v>-4.643061955306788</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.137832560681041</v>
+        <v>1.120132952208713</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1662978455568799</v>
+        <v>-0.2898924001486574</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.877935451311048</v>
+        <v>2.803778718555981</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.454140789026231</v>
+        <v>-4.49838981020705</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.205789521282376</v>
+        <v>1.188089912810048</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02162570045714246</v>
+        <v>-0.1452202550489199</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.97482684093233</v>
+        <v>2.900670108177263</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.514015616383923</v>
+        <v>-4.558264637564743</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.167877081740725</v>
+        <v>1.150177473268397</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08150052781483458</v>
+        <v>-0.2050950824066121</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.924939435919141</v>
+        <v>2.850782703164074</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.427216118604914</v>
+        <v>-4.471465139785733</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.224997374174894</v>
+        <v>1.207297765702567</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.08150052781483458</v>
+        <v>-0.2050950824066121</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.947339929241707</v>
+        <v>2.87318319648664</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.42968582506672</v>
+        <v>-4.473934846247539</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.224081892963584</v>
+        <v>1.206382284491256</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.08397023427664074</v>
+        <v>-0.2075647888684182</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.945930506738035</v>
+        <v>2.871773773982969</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.49805601139073</v>
+        <v>-4.54230503257155</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.207740740908682</v>
+        <v>1.190041132436354</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.1982890898322033</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.962502848634466</v>
+        <v>2.8883461158794</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.376639581764254</v>
+        <v>-4.420888602945073</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.246744021391164</v>
+        <v>1.229044412918836</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.1982890898322033</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.952939557266357</v>
+        <v>2.878782824511291</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.407632741092959</v>
+        <v>-4.451881762273779</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.059056322700069</v>
+        <v>1.041356714227741</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.1982890898322033</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.777649122306744</v>
+        <v>2.703492389551678</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.232158481300489</v>
+        <v>-4.276407502481309</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.133813258608844</v>
+        <v>1.116113650136517</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.1982890898322033</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.782216354298532</v>
+        <v>2.708059621543466</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.343094733941738</v>
+        <v>-4.387343755122558</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.065180786313552</v>
+        <v>1.047481177841224</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.1982890898322033</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.757958383059739</v>
+        <v>2.683801650304673</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.546121311484971</v>
+        <v>-4.590370332665791</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9871015405161641</v>
+        <v>0.9694019320438363</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.4013156673754367</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.639273821753704</v>
+        <v>2.565117088998638</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.388195712549678</v>
+        <v>-4.432444733730498</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.060444166522414</v>
+        <v>1.042744558050086</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.4013156673754367</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649446208185837</v>
+        <v>2.57528947543077</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.301952249523301</v>
+        <v>-4.34620127070412</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.089887822306825</v>
+        <v>1.072188213834497</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.4013156673754367</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644392478759698</v>
+        <v>2.570235746004631</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.303135334174362</v>
+        <v>-4.347384355355182</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.081190363890926</v>
+        <v>1.063490755418598</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.4069587158419482</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.632782425124316</v>
+        <v>2.55862569236925</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.180007627180279</v>
+        <v>-4.224256648361099</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.130993319721661</v>
+        <v>1.113293711249333</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.4069587158419482</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.633334298157417</v>
+        <v>2.559177565402351</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.087197145729419</v>
+        <v>-4.131446166910239</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.09739020419337</v>
+        <v>1.079690595721043</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1905536797993114</v>
+        <v>-0.3141482343910889</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.618293278919299</v>
+        <v>2.544136546164232</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.03863409350839</v>
+        <v>-4.082883114689209</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.118688901006383</v>
+        <v>1.100989292534055</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1419906275782812</v>
+        <v>-0.2655851821700587</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.649304586176518</v>
+        <v>2.575147853421451</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.925962875272139</v>
+        <v>-3.970211896452959</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.158833096812606</v>
+        <v>1.141133488340278</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02931940934203098</v>
+        <v>-0.1529139639338085</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.711983025629991</v>
+        <v>2.637826292874924</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.813585874089467</v>
+        <v>-3.857834895270286</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.209275193116342</v>
+        <v>1.191575584644015</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02931940934203098</v>
+        <v>-0.1529139639338085</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.717474321460658</v>
+        <v>2.643317588705592</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.011820442976197</v>
+        <v>-4.056069464157017</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.141478567330189</v>
+        <v>1.123778958857861</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2275539782287616</v>
+        <v>-0.351148532820539</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.610030781897159</v>
+        <v>2.535874049142092</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.094821724001476</v>
+        <v>-4.139070745182296</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.946633774920731</v>
+        <v>0.9289341664484032</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.3697194173477128</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.437243971181508</v>
+        <v>2.363087238426441</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.9356274519449</v>
+        <v>-3.979876473125719</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.130461144462567</v>
+        <v>1.112761535990239</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.3697194173477128</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.557393631900713</v>
+        <v>2.483236899145647</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.022226034926003</v>
+        <v>-4.066475056106823</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.110334737372449</v>
+        <v>1.092635128900121</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.3697194173477128</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.571906658003036</v>
+        <v>2.49774992524797</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.983842372367852</v>
+        <v>-4.028091393548672</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.123107643738078</v>
+        <v>1.10540803526575</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.3313357547895616</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.592356296880296</v>
+        <v>2.518199564125229</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.806726042332686</v>
+        <v>-3.850975063513506</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.190683204597446</v>
+        <v>1.172983596125118</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.3313357547895616</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.589085325725598</v>
+        <v>2.514928592970531</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.777023918356393</v>
+        <v>-3.821272939537212</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.203247445949877</v>
+        <v>1.185547837477549</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2122113254130975</v>
+        <v>-0.335805880004875</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.587086642358323</v>
+        <v>2.512929909603256</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.597648497117625</v>
+        <v>-3.641897518298444</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.268784589751798</v>
+        <v>1.25108498127947</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05543456724237883</v>
+        <v>-0.1790291218341563</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.674939672567168</v>
+        <v>2.600782939812102</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.642662710638231</v>
+        <v>-3.686911731819051</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.231586359675146</v>
+        <v>1.213886751202818</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08578346255698344</v>
+        <v>-0.2093780171487609</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.637537790709995</v>
+        <v>2.563381057954929</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.909667220910666</v>
+        <v>-3.71904796689923</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.130476117905117</v>
+        <v>1.206723819509692</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.280146500599932</v>
+        <v>-0.2098826425290135</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.526611530223172</v>
+        <v>2.568769845065723</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.198454441369582</v>
+        <v>-4.007835187358145</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.014165151618052</v>
+        <v>1.090412853222627</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.3109687626280138</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.465163780060273</v>
+        <v>2.507322094902824</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.16597885519881</v>
+        <v>-3.975359601187373</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.024755347640678</v>
+        <v>1.101003049245253</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.3109687626280138</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.46276374161459</v>
+        <v>2.504922056457141</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848103</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.146940727491512</v>
+        <v>-3.956321473480076</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.028895317931842</v>
+        <v>1.105143019536416</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.3691523739592084</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.424378294024118</v>
+        <v>2.466536608866669</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.163686592747887</v>
+        <v>-3.973067338736451</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.199778840767972</v>
+        <v>1.276026542372547</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.3691523739592084</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.601960162962799</v>
+        <v>2.64411847780535</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.216006973348679</v>
+        <v>-4.025387719337242</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.179684017513789</v>
+        <v>1.255931719118364</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.3342055139503362</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.623761607954255</v>
+        <v>2.665919922796807</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.360329879273598</v>
+        <v>-4.169710625262161</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.127963385540748</v>
+        <v>1.204211087145322</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.3342055139503362</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.629770138351181</v>
+        <v>2.671928453193733</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989909</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.212586909038595</v>
+        <v>-4.021967655027159</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.266213221426771</v>
+        <v>1.342460923031345</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.166398156715453</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.809607200484133</v>
+        <v>2.851765515326684</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651171</v>
+        <v>3.802242353651169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.314601591569817</v>
+        <v>-4.12398233755838</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.228200969945763</v>
+        <v>1.304448671550338</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.166398156715453</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.812400822015614</v>
+        <v>2.854559136858165</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864728</v>
+        <v>3.805605409864727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.177992247475724</v>
+        <v>-3.987372993464288</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.283507055975058</v>
+        <v>1.359754757579633</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1000526706922791</v>
+        <v>-0.02978881262136057</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.895028776863728</v>
+        <v>2.937187091706279</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.716619966915324</v>
+        <v>3.548751626490553</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.921549617714755</v>
+        <v>2.84051778471814</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.177992247475724</v>
+        <v>-3.987372993464288</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.283507055975058</v>
+        <v>1.359754757579633</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1000526706922791</v>
+        <v>-0.02978881262136057</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.914613414701122</v>
+        <v>2.833581581704508</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>49.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-14.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.8%</t>
+          <t>448.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-560.3%</t>
+          <t>-584.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-240.2%</t>
+          <t>-250.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.3%</t>
+          <t>-144.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-227.0%</t>
+          <t>-246.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-162.7%</t>
+          <t>-149.9%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.050603183420629</v>
+        <v>-9.053678164378555</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.504992432743963</v>
+        <v>-0.5062224251271332</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.71815395730587</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.08655787912927</v>
+        <v>2.084712890554514</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.41013350592463</v>
+        <v>-9.413208486882557</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6434542584475134</v>
+        <v>-0.644684250830684</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.71815395730587</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.09190818242732</v>
+        <v>2.090063193852564</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.460482569378852</v>
+        <v>-9.463557550336779</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6556778638720249</v>
+        <v>-0.6569078562551951</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.765428039802166</v>
+        <v>-1.768503020760092</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.069614764311964</v>
+        <v>2.067769775737208</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.67963153745305</v>
+        <v>-9.682706518410976</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7402957004799346</v>
+        <v>-0.7415256928631053</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.984577007876364</v>
+        <v>-1.98765198883429</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.941167134089214</v>
+        <v>1.939322145514459</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.675940612496639</v>
+        <v>-9.679015593454565</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7388193304973707</v>
+        <v>-0.7400493228805409</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.984577007876364</v>
+        <v>-1.98765198883429</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.941167134089214</v>
+        <v>1.939322145514459</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.880198787826503</v>
+        <v>-9.883273768784429</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8150094035106736</v>
+        <v>-0.8162393958938443</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.112215952490353</v>
+        <v>-2.115290933448279</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.870096964439463</v>
+        <v>1.868251975864708</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09823655945768</v>
+        <v>-10.10131154041561</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8977419576787082</v>
+        <v>-0.8989719500618789</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.286986720586252</v>
+        <v>-2.290061701544178</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.76971705806636</v>
+        <v>1.767872069491605</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.02476672779023</v>
+        <v>-10.02784170874816</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.852982323518308</v>
+        <v>-0.8542123159014787</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.213516888918803</v>
+        <v>-2.216591869876729</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.82917065856025</v>
+        <v>1.827325669985495</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19989114517677</v>
+        <v>-10.2029661261347</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9084768697254084</v>
+        <v>-0.9097068621085791</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.388641306305347</v>
+        <v>-2.391716287263273</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.738651228875841</v>
+        <v>1.736806240301085</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43434323919126</v>
+        <v>-10.43741822014919</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.0094768722328</v>
+        <v>-1.010706864615971</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.388641306305347</v>
+        <v>-2.391716287263273</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.731432063974245</v>
+        <v>1.729587075399489</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.7221470837285</v>
+        <v>-10.72522206468643</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.131270600821672</v>
+        <v>-1.132500593204842</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.676445150842585</v>
+        <v>-2.679520131800511</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.552077566477926</v>
+        <v>1.55023257790317</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.77493323932883</v>
+        <v>-10.77800822028676</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.151269273223246</v>
+        <v>-1.152499265606417</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.772120637424982</v>
+        <v>-2.775195618382908</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.495788064367044</v>
+        <v>1.493943075792288</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00696215906509</v>
+        <v>-11.01003714002302</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.241387112488636</v>
+        <v>-1.242617104871807</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.837208315571331</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.461274174683105</v>
+        <v>1.459429186108349</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95494664509628</v>
+        <v>-10.9580216260542</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.21659057121471</v>
+        <v>-1.217820563597881</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.837208315571331</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.465264510369505</v>
+        <v>1.46341952179475</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.0966184868204</v>
+        <v>-11.09969346777832</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.2747345348031</v>
+        <v>-1.275964527186271</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.837208315571331</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.463789283470764</v>
+        <v>1.461944294896008</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04702764239556</v>
+        <v>-11.05010262335349</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.239844786868294</v>
+        <v>-1.241074779251465</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.784542490188572</v>
+        <v>-2.787617471146497</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.508597200290536</v>
+        <v>1.506752211715781</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84787553515847</v>
+        <v>-10.85095051611639</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.173235077620137</v>
+        <v>-1.174465070003308</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.619219964238758</v>
+        <v>-2.622294945196684</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.594739582213741</v>
+        <v>1.592894593638986</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62203038243905</v>
+        <v>-10.62510536339698</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.073317943496164</v>
+        <v>-1.074547935879334</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.577293288651595</v>
+        <v>-2.58036826960952</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.629474660602248</v>
+        <v>1.627629672027493</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49745172610146</v>
+        <v>-10.50052670705939</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.022347336405069</v>
+        <v>-1.023577328788239</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.577293288651595</v>
+        <v>-2.58036826960952</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.630613805158307</v>
+        <v>1.628768816583552</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55034701414575</v>
+        <v>-10.55342199510367</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.040871677460675</v>
+        <v>-1.042101669843846</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.572337942563149</v>
+        <v>-2.575412923521074</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.636220786973482</v>
+        <v>1.634375798398727</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.266438283217</v>
+        <v>-10.26951326417493</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9215744808505395</v>
+        <v>-0.9228044732337102</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.572337942563149</v>
+        <v>-2.575412923521074</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.641954491212119</v>
+        <v>1.640109502637363</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19507189060735</v>
+        <v>-10.19814687156528</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9027651862005452</v>
+        <v>-0.9039951785837159</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.504046530911426</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.675037064384042</v>
+        <v>1.673192075809287</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.931235023403282</v>
+        <v>-9.934310004361208</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8071139206318252</v>
+        <v>-0.8083439130149959</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.504046530911426</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.665153583071135</v>
+        <v>1.663308594496379</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663993222534884</v>
+        <v>-9.667068203492811</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7020517607838399</v>
+        <v>-0.7032817531670106</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.504046530911426</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.663319022571761</v>
+        <v>1.661474033997006</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.566086183858394</v>
+        <v>-9.56916116481632</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6631892602867047</v>
+        <v>-0.6644192526698749</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.432985800092944</v>
+        <v>-2.43606078105087</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.703810157514634</v>
+        <v>1.701965168939879</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.542132642882436</v>
+        <v>-9.545207623840362</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6529393377508277</v>
+        <v>-0.6541693301339984</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.409032259116987</v>
+        <v>-2.412107240074912</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.718850788245702</v>
+        <v>1.717005799670947</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.278072704559639</v>
+        <v>-9.281147685517565</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.560575678583461</v>
+        <v>-0.5618056709666317</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.148047301752116</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.864026435077628</v>
+        <v>1.862181446502872</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570993081054802</v>
+        <v>-8.574068062012728</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.280530862841827</v>
+        <v>-0.2817608552249977</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.148047301752116</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.861239401417327</v>
+        <v>1.859394412842571</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.530808782688611</v>
+        <v>-8.533883763646537</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2641135196075095</v>
+        <v>-0.2653435119906802</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.104788022428</v>
+        <v>-2.107863003385925</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.885693604324883</v>
+        <v>1.883848615750128</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450738987150807</v>
+        <v>-8.453813968108733</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2327187801716306</v>
+        <v>-0.2339487725548013</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.024718226890196</v>
+        <v>-2.027793207848121</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.933102302868322</v>
+        <v>1.931257314293567</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.217257764921207</v>
+        <v>-8.220332745879134</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1314018624419386</v>
+        <v>-0.1326318548251093</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.791237004660597</v>
+        <v>-1.794311985618523</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.081115465043934</v>
+        <v>2.079270476469178</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067591373913693</v>
+        <v>-8.070666354871619</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07442751635189193</v>
+        <v>-0.07565750873506261</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.698333513418061</v>
+        <v>-1.701408494375987</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.133965349476496</v>
+        <v>2.132120360901741</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.935315900282807</v>
+        <v>-7.938390881240733</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02614984015251043</v>
+        <v>-0.0273798325356811</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.566058039787175</v>
+        <v>-1.5691330207451</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.208698120402055</v>
+        <v>2.2068531318273</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744716225609654</v>
+        <v>-7.74779120656758</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05290509040438707</v>
+        <v>0.05167509802121684</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.378533346071947</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.325872985893583</v>
+        <v>2.324027997318828</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495716426926073</v>
+        <v>-7.498791407883999</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1654113511014783</v>
+        <v>0.1641813587183081</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.378533346071947</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.338779327117242</v>
+        <v>2.336934338542487</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.601306416699178</v>
+        <v>-7.604381397657104</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.004800574406981895</v>
+        <v>-0.006030566790152569</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.484123335845052</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.147449403654161</v>
+        <v>2.145604415079406</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.620041318817774</v>
+        <v>-7.623116299775701</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.0362498066226653</v>
+        <v>0.03501981423949507</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.484123335845052</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.195993745531247</v>
+        <v>2.194148756956492</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.472101277410175</v>
+        <v>-7.475176258368101</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02445309950246255</v>
+        <v>-0.02568309188563278</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.460727438978569</v>
+        <v>-1.463802419936494</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.088307372388214</v>
+        <v>2.086462383813459</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.447872641021203</v>
+        <v>-7.450947621979129</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02347563120035145</v>
+        <v>-0.02470562358352213</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.439573783547522</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.094130567968119</v>
+        <v>2.092285579393364</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.404324234250512</v>
+        <v>-7.407399215208438</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01301688058716843</v>
+        <v>-0.01424687297033911</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.439573783547522</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.087169955873026</v>
+        <v>2.085324967298271</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.162175840796654</v>
+        <v>-7.16525082175458</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09830483117551791</v>
+        <v>0.09707483879234724</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.439573783547522</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.101632310254169</v>
+        <v>2.099787321679414</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.098946469028306</v>
+        <v>-7.102021449986232</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1181287003420524</v>
+        <v>0.1168987079588817</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.439573783547522</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.096164430713364</v>
+        <v>2.094319442138609</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.975655334211175</v>
+        <v>-6.978730315169101</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1649432482794815</v>
+        <v>0.1637132558963108</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.313207667772466</v>
+        <v>-1.316282648730391</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.167637205614219</v>
+        <v>2.165792217039464</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.954506135307732</v>
+        <v>-6.957581116265658</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1811039060781838</v>
+        <v>0.1798739136950136</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.295133449826948</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.188027703193611</v>
+        <v>2.186182714618855</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.710740693324287</v>
+        <v>-6.713815674282213</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2743907912186123</v>
+        <v>0.2731607988354416</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.295133449826948</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.183808411540661</v>
+        <v>2.181963422965906</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.563843665606417</v>
+        <v>-6.566918646564343</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3352739162257765</v>
+        <v>0.3340439238426063</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.24747520784836</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.21452767064783</v>
+        <v>2.212682682073075</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.313993271657342</v>
+        <v>-6.317068252615268</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4279561487891086</v>
+        <v>0.4267261564059379</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.24747520784836</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.207269745631532</v>
+        <v>2.205424757056777</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.13810117918991</v>
+        <v>-6.141176160147836</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5019121092967302</v>
+        <v>0.5006821169135596</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.24747520784836</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.210868869152181</v>
+        <v>2.209023880577426</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.966654716167446</v>
+        <v>-5.969729697125373</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5838182005602692</v>
+        <v>0.582588208177099</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.072953763867972</v>
+        <v>-1.076028744825897</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.327064253020212</v>
+        <v>2.325219264445457</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.741621716498623</v>
+        <v>-5.74469669745655</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6728518780440953</v>
+        <v>0.6716218856609251</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8479207641991487</v>
+        <v>-0.8509957451570741</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.461104530437803</v>
+        <v>2.459259541863048</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.677985974264689</v>
+        <v>-5.681060955222615</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7030009759919866</v>
+        <v>0.701770983608816</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7842850219652142</v>
+        <v>-0.7873600029231396</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.503980776832481</v>
+        <v>2.502135788257726</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.584985933058791</v>
+        <v>-5.588060914016717</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7213952512581416</v>
+        <v>0.720165258874971</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7842850219652142</v>
+        <v>-0.7873600029231396</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.485175035616277</v>
+        <v>2.483330047041521</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.34455543625393</v>
+        <v>-5.347630417211857</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.819310526604963</v>
+        <v>0.8180805342217923</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5438545251603539</v>
+        <v>-0.5469295061182793</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.63117641032407</v>
+        <v>2.629331421749315</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.272312868082736</v>
+        <v>-5.275387849040662</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.852136867708261</v>
+        <v>0.8509068753250904</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5438545251603539</v>
+        <v>-0.5469295061182793</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.63510572415889</v>
+        <v>2.633260735584135</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.15637301845755</v>
+        <v>-5.159447999415477</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8991913914756751</v>
+        <v>0.8979613990925048</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.4701077751021554</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.681877346685905</v>
+        <v>2.68003235811115</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.047568132977823</v>
+        <v>-5.05064311393575</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9397114168875595</v>
+        <v>0.9384814245043889</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.4701077751021554</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.678875417905898</v>
+        <v>2.677030429331143</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.935444747889435</v>
+        <v>-4.945929777584204</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9861398079335288</v>
+        <v>0.9819457960556215</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4494075036680273</v>
+        <v>-0.4526668649873743</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.691029629202234</v>
+        <v>2.689074012410626</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.802577058826158</v>
+        <v>-4.813062088520926</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.055181066360663</v>
+        <v>1.050987054482756</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4494075036680273</v>
+        <v>-0.4526668649873743</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.706923812004058</v>
+        <v>2.704968195212449</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.643061955306788</v>
+        <v>-4.653546985001556</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.120132952208713</v>
+        <v>1.115938940330806</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2898924001486574</v>
+        <v>-0.2931517614680044</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.803778718555981</v>
+        <v>2.801823101764373</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.49838981020705</v>
+        <v>-4.508874839901819</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.188089912810048</v>
+        <v>1.183895900932141</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1452202550489199</v>
+        <v>-0.148479616368267</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.900670108177263</v>
+        <v>2.898714491385655</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412105</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.558264637564743</v>
+        <v>-4.568749667259511</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.150177473268397</v>
+        <v>1.145983461390489</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2050950824066121</v>
+        <v>-0.2083544437259591</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.850782703164074</v>
+        <v>2.848827086372466</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.471465139785733</v>
+        <v>-4.481950169480502</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.207297765702567</v>
+        <v>1.203103753824659</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2050950824066121</v>
+        <v>-0.2083544437259591</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.87318319648664</v>
+        <v>2.871227579695032</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900694</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.473934846247539</v>
+        <v>-4.484419875942308</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.206382284491256</v>
+        <v>1.202188272613349</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2075647888684182</v>
+        <v>-0.2108241501877652</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.871773773982969</v>
+        <v>2.86981815719136</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473601</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.54230503257155</v>
+        <v>-4.552790062266318</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.190041132436354</v>
+        <v>1.185847120558447</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1982890898322033</v>
+        <v>-0.2015484511515503</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.8883461158794</v>
+        <v>2.886390499087792</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417556397837</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.420888602945073</v>
+        <v>-4.431373632639842</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.229044412918836</v>
+        <v>1.224850401040929</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1982890898322033</v>
+        <v>-0.2015484511515503</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.878782824511291</v>
+        <v>2.876827207719683</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.451881762273779</v>
+        <v>-4.462366791968547</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.041356714227741</v>
+        <v>1.037162702349833</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1982890898322033</v>
+        <v>-0.2015484511515503</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.703492389551678</v>
+        <v>2.70153677276007</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.276407502481309</v>
+        <v>-4.286892532176077</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.116113650136517</v>
+        <v>1.111919638258609</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1982890898322033</v>
+        <v>-0.2015484511515503</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.708059621543466</v>
+        <v>2.706104004751857</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.387343755122558</v>
+        <v>-4.397828784817326</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.047481177841224</v>
+        <v>1.043287165963316</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1982890898322033</v>
+        <v>-0.2015484511515503</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.683801650304673</v>
+        <v>2.681846033513064</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581292</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.590370332665791</v>
+        <v>-4.600855362360559</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9694019320438363</v>
+        <v>0.9652079201659287</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4013156673754367</v>
+        <v>-0.4045750286947837</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.565117088998638</v>
+        <v>2.56316147220703</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.432444733730498</v>
+        <v>-4.442929763425266</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.042744558050086</v>
+        <v>1.038550546172178</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4013156673754367</v>
+        <v>-0.4045750286947837</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.57528947543077</v>
+        <v>2.573333858639162</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.34620127070412</v>
+        <v>-4.356686300398889</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.072188213834497</v>
+        <v>1.06799420195659</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4013156673754367</v>
+        <v>-0.4045750286947837</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.570235746004631</v>
+        <v>2.568280129213023</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.347384355355182</v>
+        <v>-4.35786938504995</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.063490755418598</v>
+        <v>1.059296743540691</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4069587158419482</v>
+        <v>-0.4102180771612952</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.55862569236925</v>
+        <v>2.556670075577641</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.224256648361099</v>
+        <v>-4.234741678055867</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.113293711249333</v>
+        <v>1.109099699371425</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4069587158419482</v>
+        <v>-0.4102180771612952</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.559177565402351</v>
+        <v>2.557221948610743</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.131446166910239</v>
+        <v>-4.141931196605007</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.079690595721043</v>
+        <v>1.075496583843135</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3141482343910889</v>
+        <v>-0.3174075957104359</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.544136546164232</v>
+        <v>2.542180929372624</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.082883114689209</v>
+        <v>-4.093368144383978</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.100989292534055</v>
+        <v>1.096795280656148</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2655851821700587</v>
+        <v>-0.2688445434894057</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.575147853421451</v>
+        <v>2.573192236629843</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.970211896452959</v>
+        <v>-3.980696926147727</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.141133488340278</v>
+        <v>1.136939476462371</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1529139639338085</v>
+        <v>-0.1561733252531555</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.637826292874924</v>
+        <v>2.635870676083316</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.857834895270286</v>
+        <v>-3.868319924965055</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.191575584644015</v>
+        <v>1.187381572766107</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1529139639338085</v>
+        <v>-0.1561733252531555</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.643317588705592</v>
+        <v>2.641361971913983</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.056069464157017</v>
+        <v>-4.066554493851785</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.123778958857861</v>
+        <v>1.119584946979954</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.351148532820539</v>
+        <v>-0.354407894139886</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.535874049142092</v>
+        <v>2.533918432350484</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.139070745182296</v>
+        <v>-4.149555774877064</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9289341664484032</v>
+        <v>0.9247401545704959</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3697194173477128</v>
+        <v>-0.3729787786670598</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.363087238426441</v>
+        <v>2.361131621634833</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.979876473125719</v>
+        <v>-3.990361502820488</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.112761535990239</v>
+        <v>1.108567524112332</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3697194173477128</v>
+        <v>-0.3729787786670598</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.483236899145647</v>
+        <v>2.481281282354039</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660769</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.066475056106823</v>
+        <v>-4.076960085801591</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.092635128900121</v>
+        <v>1.088441117022213</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3697194173477128</v>
+        <v>-0.3729787786670598</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.49774992524797</v>
+        <v>2.495794308456362</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383424</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.028091393548672</v>
+        <v>-4.03857642324344</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.10540803526575</v>
+        <v>1.101214023387843</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3313357547895616</v>
+        <v>-0.3345951161089086</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.518199564125229</v>
+        <v>2.516243947333621</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002485</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.850975063513506</v>
+        <v>-3.861460093208274</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.172983596125118</v>
+        <v>1.168789584247211</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3313357547895616</v>
+        <v>-0.3345951161089086</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.514928592970531</v>
+        <v>2.512972976178923</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263903</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.821272939537212</v>
+        <v>-3.831757969231981</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.185547837477549</v>
+        <v>1.181353825599642</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.335805880004875</v>
+        <v>-0.339065241324222</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.512929909603256</v>
+        <v>2.510974292811648</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.641897518298444</v>
+        <v>-3.652382547993213</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.25108498127947</v>
+        <v>1.246890969401563</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1790291218341563</v>
+        <v>-0.1822884831535033</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.600782939812102</v>
+        <v>2.598827323020493</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.686911731819051</v>
+        <v>-3.697396761513819</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.213886751202818</v>
+        <v>1.20969273932491</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2093780171487609</v>
+        <v>-0.2126373784681079</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.563381057954929</v>
+        <v>2.561425441163321</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.71904796689923</v>
+        <v>-3.964401271786254</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.206723819509692</v>
+        <v>1.108582497554882</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2098826425290135</v>
+        <v>-0.4070004165110565</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.568769845065723</v>
+        <v>2.450499180676497</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230808</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.007835187358145</v>
+        <v>-4.25318849224517</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.090412853222627</v>
+        <v>0.9922715312678172</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3109687626280138</v>
+        <v>-0.5080865366100569</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.507322094902824</v>
+        <v>2.389051430513598</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285454</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.975359601187373</v>
+        <v>-4.220712906074398</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.101003049245253</v>
+        <v>1.002861727290443</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3109687626280138</v>
+        <v>-0.5080865366100569</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.504922056457141</v>
+        <v>2.386651392067915</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.956321473480076</v>
+        <v>-4.2016747783671</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.105143019536416</v>
+        <v>1.007001697581607</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3691523739592084</v>
+        <v>-0.5662701479412514</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.466536608866669</v>
+        <v>2.348265944477443</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.973067338736451</v>
+        <v>-4.218420643623475</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.276026542372547</v>
+        <v>1.177885220417737</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3691523739592084</v>
+        <v>-0.5662701479412514</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.64411847780535</v>
+        <v>2.525847813416124</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.025387719337242</v>
+        <v>-4.270741024224267</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.255931719118364</v>
+        <v>1.157790397163554</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3342055139503362</v>
+        <v>-0.5313232879323793</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.665919922796807</v>
+        <v>2.547649258407581</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.169710625262161</v>
+        <v>-4.415063930149186</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.204211087145322</v>
+        <v>1.106069765190512</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3342055139503362</v>
+        <v>-0.5313232879323793</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.671928453193733</v>
+        <v>2.553657788804507</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.021967655027159</v>
+        <v>-4.267320959914183</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.342460923031345</v>
+        <v>1.244319601076535</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.166398156715453</v>
+        <v>-0.3635159306974961</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.851765515326684</v>
+        <v>2.733494850937459</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651169</v>
+        <v>3.802242353651168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.12398233755838</v>
+        <v>-4.369335642445405</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.304448671550338</v>
+        <v>1.206307349595528</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.166398156715453</v>
+        <v>-0.3635159306974961</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.854559136858165</v>
+        <v>2.73628847246894</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864727</v>
+        <v>3.805605409864726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.987372993464288</v>
+        <v>-4.232726298351312</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.359754757579633</v>
+        <v>1.261613435624823</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.02978881262136057</v>
+        <v>-0.2269065866034036</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.937187091706279</v>
+        <v>2.818916427317053</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.548751626490553</v>
+        <v>3.772411821041111</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.84051778471814</v>
+        <v>2.967707257494296</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.987372993464288</v>
+        <v>-4.232726298351312</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.359754757579633</v>
+        <v>1.261613435624823</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.02978881262136057</v>
+        <v>-0.2269065866034036</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.833581581704508</v>
+        <v>2.960771054480664</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.3%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-584.8%</t>
+          <t>-543.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-250.1%</t>
+          <t>-233.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>-135.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-144.0%</t>
+          <t>-179.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-246.7%</t>
+          <t>-204.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-149.9%</t>
+          <t>-110.5%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.053678164378555</v>
+        <v>-9.050603183420629</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5062224251271332</v>
+        <v>-0.504992432743963</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.71815395730587</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.084712890554514</v>
+        <v>2.08655787912927</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.413208486882557</v>
+        <v>-9.41013350592463</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.644684250830684</v>
+        <v>-0.6434542584475134</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.71815395730587</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.090063193852564</v>
+        <v>2.09190818242732</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.463557550336779</v>
+        <v>-9.460482569378852</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6569078562551951</v>
+        <v>-0.6556778638720249</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.768503020760092</v>
+        <v>-1.765428039802166</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.067769775737208</v>
+        <v>2.069614764311964</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.682706518410976</v>
+        <v>-9.67963153745305</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7415256928631053</v>
+        <v>-0.7402957004799346</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.98765198883429</v>
+        <v>-1.984577007876364</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.939322145514459</v>
+        <v>1.941167134089214</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.679015593454565</v>
+        <v>-9.675940612496639</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7400493228805409</v>
+        <v>-0.7388193304973707</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.98765198883429</v>
+        <v>-1.984577007876364</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.939322145514459</v>
+        <v>1.941167134089214</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.883273768784429</v>
+        <v>-9.880198787826503</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8162393958938443</v>
+        <v>-0.8150094035106736</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.115290933448279</v>
+        <v>-2.112215952490353</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.868251975864708</v>
+        <v>1.870096964439463</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.10131154041561</v>
+        <v>-10.09823655945768</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8989719500618789</v>
+        <v>-0.8977419576787082</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.290061701544178</v>
+        <v>-2.286986720586252</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.767872069491605</v>
+        <v>1.76971705806636</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.02784170874816</v>
+        <v>-10.02476672779023</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8542123159014787</v>
+        <v>-0.852982323518308</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.216591869876729</v>
+        <v>-2.213516888918803</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.827325669985495</v>
+        <v>1.82917065856025</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.2029661261347</v>
+        <v>-10.19989114517677</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9097068621085791</v>
+        <v>-0.9084768697254084</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.391716287263273</v>
+        <v>-2.388641306305347</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.736806240301085</v>
+        <v>1.738651228875841</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43741822014919</v>
+        <v>-10.43434323919126</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.010706864615971</v>
+        <v>-1.0094768722328</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.391716287263273</v>
+        <v>-2.388641306305347</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.729587075399489</v>
+        <v>1.731432063974245</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.72522206468643</v>
+        <v>-10.7221470837285</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.132500593204842</v>
+        <v>-1.131270600821672</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.679520131800511</v>
+        <v>-2.676445150842585</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.55023257790317</v>
+        <v>1.552077566477926</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.77800822028676</v>
+        <v>-10.77493323932883</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.152499265606417</v>
+        <v>-1.151269273223246</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.775195618382908</v>
+        <v>-2.772120637424982</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.493943075792288</v>
+        <v>1.495788064367044</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.01003714002302</v>
+        <v>-11.00696215906509</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.242617104871807</v>
+        <v>-1.241387112488636</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.837208315571331</v>
+        <v>-2.834133334613405</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.459429186108349</v>
+        <v>1.461274174683105</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.9580216260542</v>
+        <v>-10.95494664509628</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.217820563597881</v>
+        <v>-1.21659057121471</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.837208315571331</v>
+        <v>-2.834133334613405</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.46341952179475</v>
+        <v>1.465264510369505</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.09969346777832</v>
+        <v>-11.0966184868204</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.275964527186271</v>
+        <v>-1.2747345348031</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.837208315571331</v>
+        <v>-2.834133334613405</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.461944294896008</v>
+        <v>1.463789283470764</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.05010262335349</v>
+        <v>-11.04702764239556</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.241074779251465</v>
+        <v>-1.239844786868294</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.787617471146497</v>
+        <v>-2.784542490188572</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.506752211715781</v>
+        <v>1.508597200290536</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.85095051611639</v>
+        <v>-10.84787553515847</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.174465070003308</v>
+        <v>-1.173235077620137</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.622294945196684</v>
+        <v>-2.619219964238758</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.592894593638986</v>
+        <v>1.594739582213741</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62510536339698</v>
+        <v>-10.62203038243905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.074547935879334</v>
+        <v>-1.073317943496164</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.58036826960952</v>
+        <v>-2.577293288651595</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.627629672027493</v>
+        <v>1.629474660602248</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.50052670705939</v>
+        <v>-10.49745172610146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.023577328788239</v>
+        <v>-1.022347336405069</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.58036826960952</v>
+        <v>-2.577293288651595</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.628768816583552</v>
+        <v>1.630613805158307</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55342199510367</v>
+        <v>-10.55034701414575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.042101669843846</v>
+        <v>-1.040871677460675</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.575412923521074</v>
+        <v>-2.572337942563149</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.634375798398727</v>
+        <v>1.636220786973482</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26951326417493</v>
+        <v>-10.266438283217</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9228044732337102</v>
+        <v>-0.9215744808505395</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.575412923521074</v>
+        <v>-2.572337942563149</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.640109502637363</v>
+        <v>1.641954491212119</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19814687156528</v>
+        <v>-10.19507189060735</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9039951785837159</v>
+        <v>-0.9027651862005452</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.504046530911426</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.673192075809287</v>
+        <v>1.675037064384042</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.934310004361208</v>
+        <v>-9.931235023403282</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8083439130149959</v>
+        <v>-0.8071139206318252</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.504046530911426</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.663308594496379</v>
+        <v>1.665153583071135</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.667068203492811</v>
+        <v>-9.663993222534884</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7032817531670106</v>
+        <v>-0.7020517607838399</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.504046530911426</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.661474033997006</v>
+        <v>1.663319022571761</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.56916116481632</v>
+        <v>-9.566086183858394</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6644192526698749</v>
+        <v>-0.6631892602867047</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.43606078105087</v>
+        <v>-2.432985800092944</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.701965168939879</v>
+        <v>1.703810157514634</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.545207623840362</v>
+        <v>-9.542132642882436</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6541693301339984</v>
+        <v>-0.6529393377508277</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.412107240074912</v>
+        <v>-2.409032259116987</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.717005799670947</v>
+        <v>1.718850788245702</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.281147685517565</v>
+        <v>-9.278072704559639</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5618056709666317</v>
+        <v>-0.560575678583461</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.148047301752116</v>
+        <v>-2.144972320794191</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.862181446502872</v>
+        <v>1.864026435077628</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.574068062012728</v>
+        <v>-8.570993081054802</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2817608552249977</v>
+        <v>-0.280530862841827</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.148047301752116</v>
+        <v>-2.144972320794191</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.859394412842571</v>
+        <v>1.861239401417327</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.533883763646537</v>
+        <v>-8.530808782688611</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2653435119906802</v>
+        <v>-0.2641135196075095</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.107863003385925</v>
+        <v>-2.104788022428</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.883848615750128</v>
+        <v>1.885693604324883</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.453813968108733</v>
+        <v>-8.354323678885867</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2339487725548013</v>
+        <v>-0.1941526568656551</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.027793207848121</v>
+        <v>-1.928302918625257</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.931257314293567</v>
+        <v>1.990951487827285</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.220332745879134</v>
+        <v>-8.12084245665627</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1326318548251093</v>
+        <v>-0.09283573913596355</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.794311985618523</v>
+        <v>-1.694821696395659</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.079270476469178</v>
+        <v>2.138964650002896</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.070666354871619</v>
+        <v>-7.971176065648755</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07565750873506261</v>
+        <v>-0.03586139304591685</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.701408494375987</v>
+        <v>-1.601918205153123</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.132120360901741</v>
+        <v>2.191814534435459</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.938390881240733</v>
+        <v>-7.838900592017868</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0273798325356811</v>
+        <v>0.01241628315346466</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.5691330207451</v>
+        <v>-1.469642731522236</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.2068531318273</v>
+        <v>2.266547305361018</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.74779120656758</v>
+        <v>-7.648300917344716</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05167509802121684</v>
+        <v>0.0914712137103626</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.378533346071947</v>
+        <v>-1.279043056849083</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.324027997318828</v>
+        <v>2.383722170852546</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.498791407883999</v>
+        <v>-7.399301118661135</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1641813587183081</v>
+        <v>0.2039774744074538</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.378533346071947</v>
+        <v>-1.279043056849083</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.336934338542487</v>
+        <v>2.396628512076205</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.604381397657104</v>
+        <v>-7.504891108434239</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.006030566790152569</v>
+        <v>0.03376554889899319</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.484123335845052</v>
+        <v>-1.384633046622187</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.145604415079406</v>
+        <v>2.205298588613124</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.623116299775701</v>
+        <v>-7.523626010552836</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03501981423949507</v>
+        <v>0.07481592992864083</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.484123335845052</v>
+        <v>-1.384633046622187</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.194148756956492</v>
+        <v>2.25384293049021</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.475176258368101</v>
+        <v>-7.375685969145237</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02568309188563278</v>
+        <v>0.01411302380351298</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.463802419936494</v>
+        <v>-1.36431213071363</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.086462383813459</v>
+        <v>2.146156557347177</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.450947621979129</v>
+        <v>-7.351457332756264</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02470562358352213</v>
+        <v>0.01509049210562363</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.439573783547522</v>
+        <v>-1.340083494324658</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.092285579393364</v>
+        <v>2.151979752927083</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.407399215208438</v>
+        <v>-7.307908925985574</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01424687297033911</v>
+        <v>0.02554924271880665</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.439573783547522</v>
+        <v>-1.340083494324658</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.085324967298271</v>
+        <v>2.14501914083199</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.16525082175458</v>
+        <v>-7.065760532531716</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09707483879234724</v>
+        <v>0.136870954481493</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.439573783547522</v>
+        <v>-1.340083494324658</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.099787321679414</v>
+        <v>2.159481495213133</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.102021449986232</v>
+        <v>-7.002531160763367</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1168987079588817</v>
+        <v>0.1566948236480274</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.439573783547522</v>
+        <v>-1.340083494324658</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.094319442138609</v>
+        <v>2.154013615672328</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.978730315169101</v>
+        <v>-6.879240025946237</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1637132558963108</v>
+        <v>0.2035093715854566</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.316282648730391</v>
+        <v>-1.216792359507527</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.165792217039464</v>
+        <v>2.225486390573183</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.957581116265658</v>
+        <v>-6.858090827042793</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1798739136950136</v>
+        <v>0.2196700293841594</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.295133449826948</v>
+        <v>-1.195643160604084</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.186182714618855</v>
+        <v>2.245876888152574</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.713815674282213</v>
+        <v>-6.614325385059349</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2731607988354416</v>
+        <v>0.3129569145245878</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.295133449826948</v>
+        <v>-1.195643160604084</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.181963422965906</v>
+        <v>2.241657596499625</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.566918646564343</v>
+        <v>-6.467428357341479</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3340439238426063</v>
+        <v>0.3738400395317516</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.24747520784836</v>
+        <v>-1.147984918625496</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.212682682073075</v>
+        <v>2.272376855606793</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.317068252615268</v>
+        <v>-6.217577963392404</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4267261564059379</v>
+        <v>0.4665222720950837</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.24747520784836</v>
+        <v>-1.147984918625496</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.205424757056777</v>
+        <v>2.265118930590496</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.141176160147836</v>
+        <v>-6.041685870924972</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5006821169135596</v>
+        <v>0.5404782326027053</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.24747520784836</v>
+        <v>-1.147984918625496</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.209023880577426</v>
+        <v>2.268718054111144</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.969729697125373</v>
+        <v>-5.870239407902509</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.582588208177099</v>
+        <v>0.6223843238662443</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.076028744825897</v>
+        <v>-0.9765384556030327</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.325219264445457</v>
+        <v>2.384913437979176</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.74469669745655</v>
+        <v>-5.645206408233686</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6716218856609251</v>
+        <v>0.7114180013500704</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8509957451570741</v>
+        <v>-0.7515054559342098</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.459259541863048</v>
+        <v>2.518953715396766</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.681060955222615</v>
+        <v>-5.581570665999751</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.701770983608816</v>
+        <v>0.7415670992979617</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7873600029231396</v>
+        <v>-0.6878697137002753</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.502135788257726</v>
+        <v>2.561829961791445</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.588060914016717</v>
+        <v>-5.488570624793853</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.720165258874971</v>
+        <v>0.7599613745641163</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7873600029231396</v>
+        <v>-0.6878697137002753</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.483330047041521</v>
+        <v>2.54302422057524</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.347630417211857</v>
+        <v>-5.248140127988993</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8180805342217923</v>
+        <v>0.857876649910938</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5469295061182793</v>
+        <v>-0.447439216895415</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.629331421749315</v>
+        <v>2.689025595283034</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.275387849040662</v>
+        <v>-5.175897559817798</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8509068753250904</v>
+        <v>0.8907029910142361</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5469295061182793</v>
+        <v>-0.447439216895415</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.633260735584135</v>
+        <v>2.692954909117854</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.159447999415477</v>
+        <v>-5.059957710192613</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8979613990925048</v>
+        <v>0.9377575147816501</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4701077751021554</v>
+        <v>-0.3706174858792911</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.68003235811115</v>
+        <v>2.739726531644868</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.05064311393575</v>
+        <v>-4.951152824712886</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9384814245043889</v>
+        <v>0.9782775401935344</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4701077751021554</v>
+        <v>-0.3706174858792911</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.677030429331143</v>
+        <v>2.736724602864862</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.945929777584204</v>
+        <v>-4.731132026675875</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9819457960556215</v>
+        <v>1.067864896418953</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4526668649873743</v>
+        <v>-0.2293976408113109</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.689074012410626</v>
+        <v>2.823035546916264</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.813062088520926</v>
+        <v>-4.598264337612598</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.050987054482756</v>
+        <v>1.136906154846087</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4526668649873743</v>
+        <v>-0.2293976408113109</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.704968195212449</v>
+        <v>2.838929729718087</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.653546985001556</v>
+        <v>-4.438749234093228</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.115938940330806</v>
+        <v>1.201858040694137</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2931517614680044</v>
+        <v>-0.06988253729194094</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.801823101764373</v>
+        <v>2.935784636270011</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.508874839901819</v>
+        <v>-4.29407708899349</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.183895900932141</v>
+        <v>1.269815001295472</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.148479616368267</v>
+        <v>0.07478960780779648</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.898714491385655</v>
+        <v>3.032676025891293</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.568749667259511</v>
+        <v>-4.353951916351183</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.145983461390489</v>
+        <v>1.231902561753821</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2083544437259591</v>
+        <v>0.01491478045010436</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.848827086372466</v>
+        <v>2.982788620878104</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.481950169480502</v>
+        <v>-4.267152418572174</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.203103753824659</v>
+        <v>1.28902285418799</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2083544437259591</v>
+        <v>0.01491478045010436</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.871227579695032</v>
+        <v>3.00518911420067</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.484419875942308</v>
+        <v>-4.26962212503398</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.202188272613349</v>
+        <v>1.28810737297668</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2108241501877652</v>
+        <v>0.01244507398829819</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.86981815719136</v>
+        <v>3.003779691696999</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.552790062266318</v>
+        <v>-4.33799231135799</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.185847120558447</v>
+        <v>1.271766220921778</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2015484511515503</v>
+        <v>0.02172077302451314</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.886390499087792</v>
+        <v>3.02035203359343</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.431373632639842</v>
+        <v>-4.216575881731513</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.224850401040929</v>
+        <v>1.31076950140426</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2015484511515503</v>
+        <v>0.02172077302451314</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.876827207719683</v>
+        <v>3.010788742225321</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.462366791968547</v>
+        <v>-4.247569041060219</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.037162702349833</v>
+        <v>1.123081802713165</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2015484511515503</v>
+        <v>0.02172077302451314</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.70153677276007</v>
+        <v>2.835498307265708</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.286892532176077</v>
+        <v>-4.072094781267749</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.111919638258609</v>
+        <v>1.19783873862194</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2015484511515503</v>
+        <v>0.02172077302451314</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.706104004751857</v>
+        <v>2.840065539257496</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695442</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.397828784817326</v>
+        <v>-4.183031033908998</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.043287165963316</v>
+        <v>1.129206266326648</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2015484511515503</v>
+        <v>0.02172077302451314</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.681846033513064</v>
+        <v>2.815807568018703</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.600855362360559</v>
+        <v>-4.191825755419166</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9652079201659287</v>
+        <v>1.128819762942486</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4045750286947837</v>
+        <v>0.01292605151434473</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.56316147220703</v>
+        <v>2.813662120332507</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.442929763425266</v>
+        <v>-4.033900156483873</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.038550546172178</v>
+        <v>1.202162388948736</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4045750286947837</v>
+        <v>0.01292605151434473</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.573333858639162</v>
+        <v>2.823834506764639</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.356686300398889</v>
+        <v>-3.947656693457495</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.06799420195659</v>
+        <v>1.231606044733147</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4045750286947837</v>
+        <v>0.01292605151434473</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.568280129213023</v>
+        <v>2.8187807773385</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.35786938504995</v>
+        <v>-3.948839778108556</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.059296743540691</v>
+        <v>1.222908586317248</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4102180771612952</v>
+        <v>0.007283003047833192</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.556670075577641</v>
+        <v>2.807170723703118</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.234741678055867</v>
+        <v>-3.825712071114473</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.109099699371425</v>
+        <v>1.272711542147983</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4102180771612952</v>
+        <v>0.007283003047833192</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.557221948610743</v>
+        <v>2.80772259673622</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.141931196605007</v>
+        <v>-3.732901589663614</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.075496583843135</v>
+        <v>1.239108426619693</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3174075957104359</v>
+        <v>0.1000934844986925</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.542180929372624</v>
+        <v>2.792681577498101</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.093368144383978</v>
+        <v>-3.684338537442583</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.096795280656148</v>
+        <v>1.260407123432706</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2688445434894057</v>
+        <v>0.1486565367197227</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.573192236629843</v>
+        <v>2.82369288475532</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.980696926147727</v>
+        <v>-3.571667319206333</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.136939476462371</v>
+        <v>1.300551319238929</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1561733252531555</v>
+        <v>0.2613277549559729</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.635870676083316</v>
+        <v>2.886371324208793</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.868319924965055</v>
+        <v>-3.45929031802366</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.187381572766107</v>
+        <v>1.350993415542665</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1561733252531555</v>
+        <v>0.2613277549559729</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.641361971913983</v>
+        <v>2.89186262003946</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.066554493851785</v>
+        <v>-3.657524886910391</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.119584946979954</v>
+        <v>1.283196789756512</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.354407894139886</v>
+        <v>0.06309318606924236</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.533918432350484</v>
+        <v>2.784419080475961</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.149555774877064</v>
+        <v>-3.74052616793567</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9247401545704959</v>
+        <v>1.088351997347053</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3729787786670598</v>
+        <v>0.0445223015420686</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.361131621634833</v>
+        <v>2.61163226976031</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.990361502820488</v>
+        <v>-3.581331895879094</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.108567524112332</v>
+        <v>1.27217936688889</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3729787786670598</v>
+        <v>0.0445223015420686</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.481281282354039</v>
+        <v>2.731781930479516</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.076960085801591</v>
+        <v>-3.667930478860197</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.088441117022213</v>
+        <v>1.252052959798772</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3729787786670598</v>
+        <v>0.0445223015420686</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.495794308456362</v>
+        <v>2.746294956581839</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.03857642324344</v>
+        <v>-3.629546816302045</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.101214023387843</v>
+        <v>1.264825866164401</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3345951161089086</v>
+        <v>0.08290596410021978</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.516243947333621</v>
+        <v>2.766744595459098</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.861460093208274</v>
+        <v>-3.452430486266879</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.168789584247211</v>
+        <v>1.332401427023769</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3345951161089086</v>
+        <v>0.08290596410021978</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.512972976178923</v>
+        <v>2.7634736243044</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.831757969231981</v>
+        <v>-3.422728362290586</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.181353825599642</v>
+        <v>1.344965668376199</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.339065241324222</v>
+        <v>0.07843583888490641</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.510974292811648</v>
+        <v>2.761474940937125</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.652382547993213</v>
+        <v>-3.243352941051818</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.246890969401563</v>
+        <v>1.410502812178121</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1822884831535033</v>
+        <v>0.2352125970556251</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.598827323020493</v>
+        <v>2.84932797114597</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.697396761513819</v>
+        <v>-3.288367154572424</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.20969273932491</v>
+        <v>1.373304582101468</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2126373784681079</v>
+        <v>0.2048637017410205</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.561425441163321</v>
+        <v>2.811926089288798</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.964401271786254</v>
+        <v>-3.555371664844859</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.108582497554882</v>
+        <v>1.27219434033144</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4070004165110565</v>
+        <v>0.0105006636980719</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.450499180676497</v>
+        <v>2.700999828801974</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.25318849224517</v>
+        <v>-3.844158885303774</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9922715312678172</v>
+        <v>1.155883374044375</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5080865366100569</v>
+        <v>-0.09058545640092847</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.389051430513598</v>
+        <v>2.639552078639075</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.220712906074398</v>
+        <v>-3.811683299133002</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.002861727290443</v>
+        <v>1.166473570067001</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5080865366100569</v>
+        <v>-0.09058545640092847</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.386651392067915</v>
+        <v>2.637152040193392</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.2016747783671</v>
+        <v>-3.792645171425705</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.007001697581607</v>
+        <v>1.170613540358165</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5662701479412514</v>
+        <v>-0.148769067732123</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.348265944477443</v>
+        <v>2.59876659260292</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.218420643623475</v>
+        <v>-3.80939103668208</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.177885220417737</v>
+        <v>1.341497063194295</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5662701479412514</v>
+        <v>-0.148769067732123</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.525847813416124</v>
+        <v>2.776348461541601</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.270741024224267</v>
+        <v>-3.861711417282872</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.157790397163554</v>
+        <v>1.321402239940112</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5313232879323793</v>
+        <v>-0.1138222077232509</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.547649258407581</v>
+        <v>2.798149906533058</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.415063930149186</v>
+        <v>-4.006034323207791</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.106069765190512</v>
+        <v>1.26968160796707</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5313232879323793</v>
+        <v>-0.1138222077232509</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.553657788804507</v>
+        <v>2.804158436929984</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.267320959914183</v>
+        <v>-3.858291352972789</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.244319601076535</v>
+        <v>1.407931443853093</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3635159306974961</v>
+        <v>0.0539851495116323</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.733494850937459</v>
+        <v>2.983995499062936</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.369335642445405</v>
+        <v>-3.96030603550401</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.206307349595528</v>
+        <v>1.369919192372086</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3635159306974961</v>
+        <v>0.0539851495116323</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.73628847246894</v>
+        <v>2.986789120594417</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864726</v>
+        <v>3.805605409864725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.232726298351312</v>
+        <v>-3.823696691409917</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.261613435624823</v>
+        <v>1.425225278401381</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2269065866034036</v>
+        <v>0.1905944936057248</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.818916427317053</v>
+        <v>3.069417075442531</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.772411821041111</v>
+        <v>3.835020239655317</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.967707257494296</v>
+        <v>3.362315817456872</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.232726298351312</v>
+        <v>-3.823696691409917</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.261613435624823</v>
+        <v>1.425225278401381</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2269065866034036</v>
+        <v>0.1905944936057248</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.960771054480664</v>
+        <v>3.35537961444324</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>61.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>-17.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>449.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-543.9%</t>
+          <t>-575.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-233.7%</t>
+          <t>-247.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-135.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-179.2%</t>
+          <t>-92.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-204.9%</t>
+          <t>-251.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-110.5%</t>
+          <t>-168.3%</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.354323678885867</v>
+        <v>-8.450738987150807</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1941526568656551</v>
+        <v>-0.2327187801716306</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.928302918625257</v>
+        <v>-2.024718226890196</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.990951487827285</v>
+        <v>1.933102302868322</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.12084245665627</v>
+        <v>-8.217257764921207</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.09283573913596355</v>
+        <v>-0.1314018624419386</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.694821696395659</v>
+        <v>-1.791237004660597</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.138964650002896</v>
+        <v>2.081115465043934</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.971176065648755</v>
+        <v>-8.067591373913693</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03586139304591685</v>
+        <v>-0.07442751635189193</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.601918205153123</v>
+        <v>-1.698333513418061</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.191814534435459</v>
+        <v>2.133965349476496</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.838900592017868</v>
+        <v>-7.935315900282807</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.01241628315346466</v>
+        <v>-0.02614984015251043</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.469642731522236</v>
+        <v>-1.566058039787175</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.266547305361018</v>
+        <v>2.208698120402055</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.648300917344716</v>
+        <v>-7.744716225609654</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.0914712137103626</v>
+        <v>0.05290509040438707</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.279043056849083</v>
+        <v>-1.375458365114022</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.383722170852546</v>
+        <v>2.325872985893583</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.399301118661135</v>
+        <v>-7.495716426926073</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2039774744074538</v>
+        <v>0.1654113511014783</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.279043056849083</v>
+        <v>-1.375458365114022</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.396628512076205</v>
+        <v>2.338779327117242</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.504891108434239</v>
+        <v>-7.601306416699178</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03376554889899319</v>
+        <v>-0.004800574406981895</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.384633046622187</v>
+        <v>-1.481048354887126</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.205298588613124</v>
+        <v>2.147449403654161</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.523626010552836</v>
+        <v>-7.620041318817774</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.07481592992864083</v>
+        <v>0.0362498066226653</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.384633046622187</v>
+        <v>-1.481048354887126</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.25384293049021</v>
+        <v>2.195993745531247</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.375685969145237</v>
+        <v>-7.472101277410175</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.01411302380351298</v>
+        <v>-0.02445309950246255</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.36431213071363</v>
+        <v>-1.460727438978569</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.146156557347177</v>
+        <v>2.088307372388214</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.351457332756264</v>
+        <v>-7.447872641021203</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01509049210562363</v>
+        <v>-0.02347563120035145</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.340083494324658</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.151979752927083</v>
+        <v>2.094130567968119</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.307908925985574</v>
+        <v>-7.404324234250512</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02554924271880665</v>
+        <v>-0.01301688058716843</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.340083494324658</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.14501914083199</v>
+        <v>2.087169955873026</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.065760532531716</v>
+        <v>-7.162175840796654</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.136870954481493</v>
+        <v>0.09830483117551791</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.340083494324658</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.159481495213133</v>
+        <v>2.101632310254169</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.002531160763367</v>
+        <v>-7.098946469028306</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1566948236480274</v>
+        <v>0.1181287003420524</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.340083494324658</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.154013615672328</v>
+        <v>2.096164430713364</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.879240025946237</v>
+        <v>-6.975655334211175</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2035093715854566</v>
+        <v>0.1649432482794815</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.216792359507527</v>
+        <v>-1.313207667772466</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.225486390573183</v>
+        <v>2.167637205614219</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.858090827042793</v>
+        <v>-6.954506135307732</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2196700293841594</v>
+        <v>0.1811039060781838</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.195643160604084</v>
+        <v>-1.292058468869023</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.245876888152574</v>
+        <v>2.188027703193611</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.614325385059349</v>
+        <v>-6.710740693324287</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3129569145245878</v>
+        <v>0.2743907912186123</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.195643160604084</v>
+        <v>-1.292058468869023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.241657596499625</v>
+        <v>2.183808411540661</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.467428357341479</v>
+        <v>-6.563843665606417</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3738400395317516</v>
+        <v>0.3352739162257765</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.147984918625496</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.272376855606793</v>
+        <v>2.21452767064783</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.217577963392404</v>
+        <v>-6.313993271657342</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4665222720950837</v>
+        <v>0.4279561487891086</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.147984918625496</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.265118930590496</v>
+        <v>2.207269745631532</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.041685870924972</v>
+        <v>-6.13810117918991</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5404782326027053</v>
+        <v>0.5019121092967302</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.147984918625496</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.268718054111144</v>
+        <v>2.210868869152181</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.870239407902509</v>
+        <v>-5.966654716167446</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6223843238662443</v>
+        <v>0.5838182005602692</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9765384556030327</v>
+        <v>-1.072953763867972</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.384913437979176</v>
+        <v>2.327064253020212</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.645206408233686</v>
+        <v>-5.741621716498623</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7114180013500704</v>
+        <v>0.6728518780440953</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7515054559342098</v>
+        <v>-0.8479207641991487</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.518953715396766</v>
+        <v>2.461104530437803</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.581570665999751</v>
+        <v>-5.677985974264689</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7415670992979617</v>
+        <v>0.7030009759919866</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6878697137002753</v>
+        <v>-0.7842850219652142</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.561829961791445</v>
+        <v>2.503980776832481</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.488570624793853</v>
+        <v>-5.584985933058791</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7599613745641163</v>
+        <v>0.7213952512581416</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6878697137002753</v>
+        <v>-0.7842850219652142</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.54302422057524</v>
+        <v>2.485175035616277</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.248140127988993</v>
+        <v>-5.34455543625393</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.857876649910938</v>
+        <v>0.819310526604963</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.447439216895415</v>
+        <v>-0.5438545251603539</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.689025595283034</v>
+        <v>2.63117641032407</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.175897559817798</v>
+        <v>-5.272312868082736</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8907029910142361</v>
+        <v>0.852136867708261</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.447439216895415</v>
+        <v>-0.5438545251603539</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.692954909117854</v>
+        <v>2.63510572415889</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349963</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.059957710192613</v>
+        <v>-5.15637301845755</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9377575147816501</v>
+        <v>0.8991913914756751</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3706174858792911</v>
+        <v>-0.46703279414423</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.739726531644868</v>
+        <v>2.681877346685905</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.951152824712886</v>
+        <v>-5.047568132977823</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9782775401935344</v>
+        <v>0.9397114168875595</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3706174858792911</v>
+        <v>-0.46703279414423</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.736724602864862</v>
+        <v>2.678875417905898</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.731132026675875</v>
+        <v>-4.827547334940813</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.067864896418953</v>
+        <v>1.029298773112978</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2293976408113109</v>
+        <v>-0.3258129490762498</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.823035546916264</v>
+        <v>2.7651863619573</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.598264337612598</v>
+        <v>-4.722269260028706</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.136906154846087</v>
+        <v>1.087304185879644</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2293976408113109</v>
+        <v>-0.3258129490762498</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.838929729718087</v>
+        <v>2.781080544759124</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.438749234093228</v>
+        <v>-4.562754156509336</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.201858040694137</v>
+        <v>1.152256071727694</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06988253729194094</v>
+        <v>-0.1662978455568799</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.935784636270011</v>
+        <v>2.877935451311048</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.29407708899349</v>
+        <v>-4.418082011409599</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.269815001295472</v>
+        <v>1.220213032329029</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.07478960780779648</v>
+        <v>-0.02162570045714246</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.032676025891293</v>
+        <v>2.97482684093233</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.353951916351183</v>
+        <v>-4.477956838767291</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.231902561753821</v>
+        <v>1.182300592787378</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.01491478045010436</v>
+        <v>-0.08150052781483458</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.982788620878104</v>
+        <v>2.924939435919141</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.267152418572174</v>
+        <v>-4.391157340988283</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.28902285418799</v>
+        <v>1.239420885221547</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.01491478045010436</v>
+        <v>-0.08150052781483458</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.00518911420067</v>
+        <v>2.947339929241707</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.26962212503398</v>
+        <v>-4.393627047450089</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.28810737297668</v>
+        <v>1.238505404010237</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.01244507398829819</v>
+        <v>-0.08397023427664074</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.003779691696999</v>
+        <v>2.945930506738035</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.33799231135799</v>
+        <v>-4.461997233774099</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.271766220921778</v>
+        <v>1.222164251955335</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02172077302451314</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.02035203359343</v>
+        <v>2.962502848634466</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.216575881731513</v>
+        <v>-4.340580804147622</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.31076950140426</v>
+        <v>1.261167532437816</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02172077302451314</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.010788742225321</v>
+        <v>2.952939557266357</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.247569041060219</v>
+        <v>-4.371573963476328</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.123081802713165</v>
+        <v>1.073479833746721</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02172077302451314</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.835498307265708</v>
+        <v>2.777649122306744</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.072094781267749</v>
+        <v>-4.196099703683858</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.19783873862194</v>
+        <v>1.148236769655497</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02172077302451314</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.840065539257496</v>
+        <v>2.782216354298532</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.183031033908998</v>
+        <v>-4.307035956325107</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.129206266326648</v>
+        <v>1.079604297360204</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02172077302451314</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.815807568018703</v>
+        <v>2.757958383059739</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.191825755419166</v>
+        <v>-4.51006253386834</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.128819762942486</v>
+        <v>1.001525051562816</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.01292605151434473</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.813662120332507</v>
+        <v>2.639273821753704</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.033900156483873</v>
+        <v>-4.352136934933047</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.202162388948736</v>
+        <v>1.074867677569066</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.01292605151434473</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.823834506764639</v>
+        <v>2.649446208185837</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.947656693457495</v>
+        <v>-4.265893471906669</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.231606044733147</v>
+        <v>1.104311333353478</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.01292605151434473</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.8187807773385</v>
+        <v>2.644392478759698</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.948839778108556</v>
+        <v>-4.267076556557731</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.222908586317248</v>
+        <v>1.095613874937579</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.007283003047833192</v>
+        <v>-0.2833641612501707</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.807170723703118</v>
+        <v>2.632782425124316</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.825712071114473</v>
+        <v>-4.143948849563648</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.272711542147983</v>
+        <v>1.145416830768313</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.007283003047833192</v>
+        <v>-0.2833641612501707</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.80772259673622</v>
+        <v>2.633334298157417</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.732901589663614</v>
+        <v>-4.051138368112788</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.239108426619693</v>
+        <v>1.111813715240023</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.1000934844986925</v>
+        <v>-0.1905536797993114</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.792681577498101</v>
+        <v>2.618293278919299</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.684338537442583</v>
+        <v>-4.002575315891757</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.260407123432706</v>
+        <v>1.133112412053036</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.1486565367197227</v>
+        <v>-0.1419906275782812</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.82369288475532</v>
+        <v>2.649304586176518</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.571667319206333</v>
+        <v>-3.889904097655507</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.300551319238929</v>
+        <v>1.173256607859259</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2613277549559729</v>
+        <v>-0.02931940934203098</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.886371324208793</v>
+        <v>2.711983025629991</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.45929031802366</v>
+        <v>-3.777527096472835</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.350993415542665</v>
+        <v>1.223698704162995</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2613277549559729</v>
+        <v>-0.02931940934203098</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.89186262003946</v>
+        <v>2.717474321460658</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.657524886910391</v>
+        <v>-3.975761665359565</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.283196789756512</v>
+        <v>1.155902078376842</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.06309318606924236</v>
+        <v>-0.2275539782287616</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.784419080475961</v>
+        <v>2.610030781897159</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.74052616793567</v>
+        <v>-4.058762946384844</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.088351997347053</v>
+        <v>0.9610572859673838</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.0445223015420686</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.61163226976031</v>
+        <v>2.437243971181508</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.581331895879094</v>
+        <v>-3.899568674328268</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.27217936688889</v>
+        <v>1.14488465550922</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.0445223015420686</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.731781930479516</v>
+        <v>2.557393631900713</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.667930478860197</v>
+        <v>-3.986167257309371</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.252052959798772</v>
+        <v>1.124758248419102</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.0445223015420686</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.746294956581839</v>
+        <v>2.571906658003036</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.629546816302045</v>
+        <v>-3.94778359475122</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.264825866164401</v>
+        <v>1.137531154784731</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.08290596410021978</v>
+        <v>-0.2077412001977841</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.766744595459098</v>
+        <v>2.592356296880296</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.452430486266879</v>
+        <v>-3.770667264716054</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.332401427023769</v>
+        <v>1.205106715644099</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.08290596410021978</v>
+        <v>-0.2077412001977841</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.7634736243044</v>
+        <v>2.589085325725598</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.422728362290586</v>
+        <v>-3.74096514073976</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.344965668376199</v>
+        <v>1.21767095699653</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.07843583888490641</v>
+        <v>-0.2122113254130975</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.761474940937125</v>
+        <v>2.587086642358323</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.243352941051818</v>
+        <v>-3.561589719500992</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.410502812178121</v>
+        <v>1.283208100798451</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.2352125970556251</v>
+        <v>-0.05543456724237883</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.84932797114597</v>
+        <v>2.674939672567168</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.288367154572424</v>
+        <v>-3.606603933021598</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.373304582101468</v>
+        <v>1.246009870721799</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.2048637017410205</v>
+        <v>-0.08578346255698344</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.811926089288798</v>
+        <v>2.637537790709995</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979534</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.555371664844859</v>
+        <v>-3.873608443294033</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.27219434033144</v>
+        <v>1.14489962895177</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.0105006636980719</v>
+        <v>-0.280146500599932</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.700999828801974</v>
+        <v>2.526611530223172</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.844158885303774</v>
+        <v>-3.92967351974408</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.155883374044375</v>
+        <v>1.121677520268253</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.09058545640092847</v>
+        <v>-0.3264862045990564</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.639552078639075</v>
+        <v>2.498011629720199</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.811683299133002</v>
+        <v>-3.897197933573307</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.166473570067001</v>
+        <v>1.132267716290879</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.09058545640092847</v>
+        <v>-0.3264862045990564</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.637152040193392</v>
+        <v>2.495611591274515</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.792645171425705</v>
+        <v>-3.87815980586601</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.170613540358165</v>
+        <v>1.136407686582043</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.148769067732123</v>
+        <v>-0.384669815930251</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.59876659260292</v>
+        <v>2.457226143684044</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.80939103668208</v>
+        <v>-3.894905671122385</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.341497063194295</v>
+        <v>1.307291209418173</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.148769067732123</v>
+        <v>-0.384669815930251</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.776348461541601</v>
+        <v>2.634808012622724</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.861711417282872</v>
+        <v>-3.947226051723177</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.321402239940112</v>
+        <v>1.28719638616399</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.1138222077232509</v>
+        <v>-0.3497229559213788</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.798149906533058</v>
+        <v>2.656609457614181</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259121</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.006034323207791</v>
+        <v>-4.091548957648095</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.26968160796707</v>
+        <v>1.235475754190948</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.1138222077232509</v>
+        <v>-0.3497229559213788</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.804158436929984</v>
+        <v>2.662617988011107</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989906</v>
+        <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.858291352972789</v>
+        <v>-3.943805987413093</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.407931443853093</v>
+        <v>1.373725590076971</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.0539851495116323</v>
+        <v>-0.1819155986864956</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.983995499062936</v>
+        <v>2.842455050144059</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651168</v>
+        <v>3.802242353651171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.96030603550401</v>
+        <v>-4.045820669944314</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.369919192372086</v>
+        <v>1.335713338595964</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.0539851495116323</v>
+        <v>-0.1819155986864956</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.986789120594417</v>
+        <v>2.84524867167554</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864725</v>
+        <v>3.80560540986473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.823696691409917</v>
+        <v>-3.909211325850222</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.425225278401381</v>
+        <v>1.391019424625259</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1905944936057248</v>
+        <v>-0.04530625459240317</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.069417075442531</v>
+        <v>2.927876626523654</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.835020239655317</v>
+        <v>3.893474732868086</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.362315817456872</v>
+        <v>2.940332565144295</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.823696691409917</v>
+        <v>-4.134982702064507</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.425225278401381</v>
+        <v>1.285983060004745</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1905944936057248</v>
+        <v>-0.2710776308066884</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.35537961444324</v>
+        <v>2.777685986660282</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240519.xlsx
+++ b/tame_output/ON/bt/strategyON_20240519.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.1%</t>
+          <t>-574.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-247.6%</t>
+          <t>-245.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>-92.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.1%</t>
+          <t>-251.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.3%</t>
+          <t>-167.2%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781948</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.722269260028706</v>
+        <v>-4.694679645877535</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.087304185879644</v>
+        <v>1.098340031540112</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.562754156509336</v>
+        <v>-4.535164542358165</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.152256071727694</v>
+        <v>1.163291917388162</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.418082011409599</v>
+        <v>-4.390492397258428</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.220213032329029</v>
+        <v>1.231248877989497</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.477956838767291</v>
+        <v>-4.45036722461612</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.182300592787378</v>
+        <v>1.193336438447846</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.391157340988283</v>
+        <v>-4.363567726837111</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.239420885221547</v>
+        <v>1.250456730882016</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.393627047450089</v>
+        <v>-4.366037433298917</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.238505404010237</v>
+        <v>1.249541249670705</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.461997233774099</v>
+        <v>-4.434407619622927</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.222164251955335</v>
+        <v>1.233200097615803</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.340580804147622</v>
+        <v>-4.312991189996451</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.261167532437816</v>
+        <v>1.272203378098285</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.371573963476328</v>
+        <v>-4.343984349325156</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.073479833746721</v>
+        <v>1.08451567940719</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.196099703683858</v>
+        <v>-4.168510089532687</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.148236769655497</v>
+        <v>1.159272615315965</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.307035956325107</v>
+        <v>-4.279446342173935</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.079604297360204</v>
+        <v>1.090640143020673</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.51006253386834</v>
+        <v>-4.482472919717169</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.001525051562816</v>
+        <v>1.012560897223285</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.352136934933047</v>
+        <v>-4.324547320781876</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.074867677569066</v>
+        <v>1.085903523229535</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.265893471906669</v>
+        <v>-4.238303857755498</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.104311333353478</v>
+        <v>1.115347179013946</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.267076556557731</v>
+        <v>-4.239486942406559</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.095613874937579</v>
+        <v>1.106649720598047</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.143948849563648</v>
+        <v>-4.116359235412476</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.145416830768313</v>
+        <v>1.156452676428782</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.051138368112788</v>
+        <v>-4.023548753961617</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.111813715240023</v>
+        <v>1.122849560900491</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.002575315891757</v>
+        <v>-3.974985701740586</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.133112412053036</v>
+        <v>1.144148257713504</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.889904097655507</v>
+        <v>-3.862314483504336</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.173256607859259</v>
+        <v>1.184292453519727</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.777527096472835</v>
+        <v>-3.749937482321664</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.223698704162995</v>
+        <v>1.234734549823464</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.975761665359565</v>
+        <v>-3.948172051208394</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.155902078376842</v>
+        <v>1.166937924037311</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.058762946384844</v>
+        <v>-4.031173332233672</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9610572859673838</v>
+        <v>0.9720931316278525</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.899568674328268</v>
+        <v>-3.871979060177096</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.14488465550922</v>
+        <v>1.155920501169688</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660769</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.986167257309371</v>
+        <v>-3.958577643158199</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.124758248419102</v>
+        <v>1.13579409407957</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383424</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.94778359475122</v>
+        <v>-3.920193980600048</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.137531154784731</v>
+        <v>1.1485670004452</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002485</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.770667264716054</v>
+        <v>-3.743077650564882</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.205106715644099</v>
+        <v>1.216142561304568</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263903</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.74096514073976</v>
+        <v>-3.713375526588588</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.21767095699653</v>
+        <v>1.228706802656998</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.561589719500992</v>
+        <v>-3.53400010534982</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.283208100798451</v>
+        <v>1.29424394645892</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.606603933021598</v>
+        <v>-3.579014318870426</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.246009870721799</v>
+        <v>1.257045716382267</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.873608443294033</v>
+        <v>-3.846018829142862</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.14489962895177</v>
+        <v>1.155935474612239</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.280146500599932</v>
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.92967351974408</v>
+        <v>-3.91831175440313</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.121677520268253</v>
+        <v>1.126222226404633</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3264862045990564</v>
+        <v>-0.3308358068302577</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.498011629720199</v>
+        <v>2.495401868381478</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.897197933573307</v>
+        <v>-3.885836168232358</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.132267716290879</v>
+        <v>1.136812422427259</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3264862045990564</v>
+        <v>-0.3308358068302577</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.495611591274515</v>
+        <v>2.493001829935795</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848103</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.87815980586601</v>
+        <v>-3.86679804052506</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.136407686582043</v>
+        <v>1.140952392718423</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.384669815930251</v>
+        <v>-0.3890194181614522</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.457226143684044</v>
+        <v>2.454616382345323</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.894905671122385</v>
+        <v>-3.883543905781436</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.307291209418173</v>
+        <v>1.311835915554553</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.384669815930251</v>
+        <v>-0.3890194181614522</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.634808012622724</v>
+        <v>2.632198251284004</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.947226051723177</v>
+        <v>-3.935864286382227</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.28719638616399</v>
+        <v>1.29174109230037</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3497229559213788</v>
+        <v>-0.35407255815258</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.656609457614181</v>
+        <v>2.65399969627546</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.091548957648095</v>
+        <v>-4.080187192307146</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.235475754190948</v>
+        <v>1.240020460327328</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3497229559213788</v>
+        <v>-0.35407255815258</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.662617988011107</v>
+        <v>2.660008226672386</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989909</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.943805987413093</v>
+        <v>-3.932444222072144</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.373725590076971</v>
+        <v>1.378270296213351</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1819155986864956</v>
+        <v>-0.1862652009176969</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.842455050144059</v>
+        <v>2.839845288805338</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651171</v>
+        <v>3.802242353651169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.045820669944314</v>
+        <v>-4.034458904603365</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.335713338595964</v>
+        <v>1.340258044732344</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1819155986864956</v>
+        <v>-0.1862652009176969</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.84524867167554</v>
+        <v>2.842638910336819</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560540986473</v>
+        <v>3.805605409864728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.909211325850222</v>
+        <v>-3.897849560509272</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.391019424625259</v>
+        <v>1.395564130761639</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.04530625459240317</v>
+        <v>-0.04965585682360441</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.927876626523654</v>
+        <v>2.925266865184933</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.893474732868086</v>
+        <v>3.893474732868084</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.940332565144295</v>
+        <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.134982702064507</v>
+        <v>-4.12479641990728</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.285983060004745</v>
+        <v>1.303865863742546</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2710776308066884</v>
+        <v>-0.2766027162216121</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.777685986660282</v>
+        <v>2.788179226286239</v>
       </c>
     </row>
   </sheetData>
